--- a/Files/Madden26/IE/Season2/FreeAgency/Output/ContractOffer.xlsx
+++ b/Files/Madden26/IE/Season2/FreeAgency/Output/ContractOffer.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,22 +429,22 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Team</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Player</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Contract</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>IsSigned</t>
         </is>
@@ -446,7 +458,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>00100000111111000000100011100000</t>
+          <t>00100000111111000000000111100100</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -456,7 +468,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -468,7 +480,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>00100000111111000000101000101101</t>
+          <t>00100000111111000000100101000010</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -478,7 +490,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -490,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>00100000111111000000100011110010</t>
+          <t>00100000111111000000000011011010</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -500,7 +512,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -512,7 +524,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>00100000111111000000001100110011</t>
+          <t>00100000111111000000100011001001</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -522,7 +534,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -534,7 +546,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>00100000111111000000011111011001</t>
+          <t>00100000111111000000000111010111</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -544,7 +556,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -556,7 +568,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>00100000111111000000100111011001</t>
+          <t>00100000111111000000100111100100</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -566,7 +578,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -578,7 +590,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>00100000111111000000010011111000</t>
+          <t>00100000111111000000011101000100</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -588,19 +600,19 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>00101110001110100000000000000001</t>
+          <t>00101110001110100000000000000010</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>00100000111111000000010100011001</t>
+          <t>00100000111111000000010011111111</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -610,19 +622,19 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>00101110001110100000000000000010</t>
+          <t>00101110001110100000000000000001</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>00100000111111000000000101010100</t>
+          <t>00100000111111000000000110100100</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -632,19 +644,19 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>00101110001110100000000000000010</t>
+          <t>00101110001110100000000000000001</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>00100000111111000000010101100000</t>
+          <t>00100000111111000000000100011011</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -654,7 +666,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -666,7 +678,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>00100000111111000000001110000011</t>
+          <t>00100000111111000000001111101001</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -676,7 +688,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -688,7 +700,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>00100000111111000000100010000101</t>
+          <t>00100000111111000000011110110111</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -698,7 +710,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -710,7 +722,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>00100000111111000000000110110000</t>
+          <t>00100000111111000000001011001011</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -720,7 +732,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -732,7 +744,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>00100000111111000000001010101001</t>
+          <t>00100000111111000000101000001110</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -742,7 +754,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -754,7 +766,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>00100000111111000000000010001111</t>
+          <t>00100000111111000000101010000100</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -764,7 +776,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -776,7 +788,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>00100000111111000000101000001110</t>
+          <t>00100000111111000000101001010111</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -786,7 +798,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -798,7 +810,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>00100000111111000000011110010101</t>
+          <t>00100000111111000000100110011110</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -808,7 +820,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -820,7 +832,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>00100000111111000000011011011111</t>
+          <t>00100000111111000000100011001110</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -830,7 +842,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -842,7 +854,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>00100000111111000000001010010010</t>
+          <t>00100000111111000000101111011010</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -852,19 +864,19 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>00101110001110100000000000000011</t>
+          <t>00101110001110100000000000000010</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>00100000111111000000101010111010</t>
+          <t>00100000111111000000101010010101</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -886,7 +898,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>00100000111111000000010101111101</t>
+          <t>00100000111111000000100010001111</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -896,19 +908,19 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>00101110001110100000000000000101</t>
+          <t>00101110001110100000000000000100</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>00100000111111000000001110110000</t>
+          <t>00100000111111000000011011101110</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -918,19 +930,19 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>00101110001110100000000000000101</t>
+          <t>00101110001110100000000000000100</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>00100000111111000000000111100100</t>
+          <t>00100000111111000000000001100011</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -940,19 +952,19 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>00101110001110100000000000000101</t>
+          <t>00101110001110100000000000000100</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>00100000111111000000000101101100</t>
+          <t>00100000111111000000001101000110</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -962,19 +974,19 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>00101110001110100000000000000101</t>
+          <t>00101110001110100000000000000100</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>00100000111111000000000001111111</t>
+          <t>00100000111111000000011010100000</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -984,19 +996,19 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>00101110001110100000000000000101</t>
+          <t>00101110001110100000000000000100</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>00100000111111000000010111100010</t>
+          <t>00100000111111000000011010111110</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1006,19 +1018,19 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>00101110001110100000000000000101</t>
+          <t>00101110001110100000000000000001</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>00100000111111000000100001110010</t>
+          <t>00100000111111000000011110010110</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1028,19 +1040,19 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>00101110001110100000000000000101</t>
+          <t>00101110001110100000000000000001</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>00100000111111000000010011110110</t>
+          <t>00100000111111000000000100100001</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1050,7 +1062,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1062,7 +1074,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>00100000111111000000100011110110</t>
+          <t>00100000111111000000001011110000</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1072,7 +1084,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1096,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>00100000111111000000100110011110</t>
+          <t>00100000111111000000000000101011</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1094,19 +1106,19 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>00101110001110100000000000000110</t>
+          <t>00101110001110100000000000000001</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>00100000111111000000010011100111</t>
+          <t>00100000111111000000011111001101</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1116,19 +1128,19 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>00101110001110100000000000000110</t>
+          <t>00101110001110100000000000000101</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>00100000111111000000000000000110</t>
+          <t>00100000111111000000101011110100</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1138,19 +1150,19 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>00101110001110100000000000000110</t>
+          <t>00101110001110100000000000000101</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>00100000111111000000011001000101</t>
+          <t>00100000111111000000010101010011</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1160,19 +1172,19 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>00101110001110100000000000000110</t>
+          <t>00101110001110100000000000000101</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>00100000111111000000000111100100</t>
+          <t>00100000111111000000100001001110</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1182,19 +1194,19 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>00101110001110100000000000000110</t>
+          <t>00101110001110100000000000000101</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>00100000111111000000101100111000</t>
+          <t>00100000111111000000101111000000</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1204,19 +1216,19 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>00101110001110100000000000000110</t>
+          <t>00101110001110100000000000000101</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>00100000111111000000100110011010</t>
+          <t>00100000111111000000011011011111</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1226,19 +1238,19 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>00101110001110100000000000000110</t>
+          <t>00101110001110100000000000000010</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>00100000111111000000101110111000</t>
+          <t>00100000111111000000010011000000</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1260,7 +1272,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>00100000111111000000001001011000</t>
+          <t>00100000111111000000011111010011</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1270,7 +1282,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1294,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>00100000111111000000100110000110</t>
+          <t>00100000111111000000000101011010</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1292,7 +1304,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1316,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>00100000111111000000101010010101</t>
+          <t>00100000111111000000010010111100</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1314,19 +1326,19 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>00101110001110100000000000000111</t>
+          <t>00101110001110100000000000000110</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>00100000111111000000100000000011</t>
+          <t>00100000111111000000011101100000</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1336,19 +1348,19 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>00101110001110100000000000000111</t>
+          <t>00101110001110100000000000000110</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>00100000111111000000010011010100</t>
+          <t>00100000111111000000100000010011</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1358,19 +1370,19 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>00101110001110100000000000000111</t>
+          <t>00101110001110100000000000000110</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>00100000111111000000011000110101</t>
+          <t>00100000111111000000011000010110</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1380,7 +1392,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1392,7 +1404,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>00100000111111000000010100000101</t>
+          <t>00100000111111000000101000011110</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1402,7 +1414,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1414,7 +1426,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>00100000111111000000001000010111</t>
+          <t>00100000111111000000100001011101</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1424,7 +1436,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1448,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>00100000111111000000000111100100</t>
+          <t>00100000111111000000100101001001</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1446,19 +1458,19 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>00101110001110100000000000000111</t>
+          <t>00101110001110100000000000000001</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>00100000111111000000000010011110</t>
+          <t>00100000111111000000001110110111</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1468,7 +1480,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1480,7 +1492,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>00100000111111000000010011110110</t>
+          <t>00100000111111000000001101111100</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1490,7 +1502,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1514,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>00100000111111000000100010000101</t>
+          <t>00100000111111000000101001100101</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1512,19 +1524,19 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>00101110001110100000000000000111</t>
+          <t>00101110001110100000000000000010</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>00100000111111000000010101010011</t>
+          <t>00100000111111000000000001011000</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -1541,12 +1553,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>00101110001110100000000000001010</t>
+          <t>00101110001110100000000000000010</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>00100000111111000000101101001011</t>
+          <t>00100000111111000000000111010101</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -1563,12 +1575,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>00101110001110100000000000001010</t>
+          <t>00101110001110100000000000000111</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>00100000111111000000011010111110</t>
+          <t>00100000111111000000010110001101</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -1578,19 +1590,19 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>00101110001110100000000000001011</t>
+          <t>00101110001110100000000000000010</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>00100000111111000000000000011110</t>
+          <t>00100000111111000000011001110111</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -1600,19 +1612,19 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>00101110001110100000000000001011</t>
+          <t>00101110001110100000000000000010</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>00100000111111000000100100010010</t>
+          <t>00100000111111000000010101110101</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -1629,12 +1641,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>00101110001110100000000000001011</t>
+          <t>00101110001110100000000000001010</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>00100000111111000000000011110100</t>
+          <t>00100000111111000000001010101001</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -1644,19 +1656,19 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>00101110001110100000000000001011</t>
+          <t>00101110001110100000000000000101</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>00100000111111000000001011001101</t>
+          <t>00100000111111000000001010101000</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -1673,12 +1685,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>00101110001110100000000000001100</t>
+          <t>00101110001110100000000000001010</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>00100000111111000000000101101100</t>
+          <t>00100000111111000000001001111001</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -1688,19 +1700,19 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>00101110001110100000000000001100</t>
+          <t>00101110001110100000000000001011</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>00100000111111000000000110110000</t>
+          <t>00100000111111000000010111000001</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -1710,19 +1722,19 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>00101110001110100000000000001100</t>
+          <t>00101110001110100000000000001011</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>00100000111111000000101011010011</t>
+          <t>00100000111111000000011101100111</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -1732,19 +1744,19 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>00101110001110100000000000001100</t>
+          <t>00101110001110100000000000001011</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>00100000111111000000011100110101</t>
+          <t>00100000111111000000100000100110</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -1754,19 +1766,19 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>00101110001110100000000000001100</t>
+          <t>00101110001110100000000000001011</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>00100000111111000000011111101110</t>
+          <t>00100000111111000000100111111110</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -1776,19 +1788,19 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>00101110001110100000000000001110</t>
+          <t>00101110001110100000000000000010</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>00100000111111000000001101110001</t>
+          <t>00100000111111000000011001000100</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -1798,19 +1810,19 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>00101110001110100000000000001110</t>
+          <t>00101110001110100000000000001100</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>00100000111111000000000111100100</t>
+          <t>00100000111111000000000100000001</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -1820,19 +1832,19 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>00101110001110100000000000001111</t>
+          <t>00101110001110100000000000001100</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>00100000111111000000001000010111</t>
+          <t>00100000111111000000011100011001</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -1842,19 +1854,19 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>00101110001110100000000000001111</t>
+          <t>00101110001110100000000000000010</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>00100000111111000000010111001101</t>
+          <t>00100000111111000000000000101100</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -1864,19 +1876,19 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>00101110001110100000000000001111</t>
+          <t>00101110001110100000000000000010</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>00100000111111000000000101101100</t>
+          <t>00100000111111000000001110000011</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -1886,7 +1898,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1898,7 +1910,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>00100000111111000000000110000111</t>
+          <t>00100000111111000000000001111111</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -1908,19 +1920,19 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>00101110001110100000000000001111</t>
+          <t>00101110001110100000000000000010</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>00100000111111000000001000010000</t>
+          <t>00100000111111000000101100111000</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -1930,7 +1942,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1942,7 +1954,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>00100000111111000000011111111011</t>
+          <t>00100000111111000000101000010111</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -1952,19 +1964,19 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>00101110001110100000000000001111</t>
+          <t>00101110001110100000000000000010</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>00100000111111000000000010111000</t>
+          <t>00100000111111000000010010011010</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -1974,7 +1986,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1986,7 +1998,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>00100000111111000000010101000001</t>
+          <t>00100000111111000000000101101100</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -1996,19 +2008,19 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>00101110001110100000000000010000</t>
+          <t>00101110001110100000000000001111</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>00100000111111000000001011001101</t>
+          <t>00100000111111000000100010000010</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -2018,7 +2030,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -2030,7 +2042,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>00100000111111000000000000010000</t>
+          <t>00100000111111000000101100110010</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -2040,7 +2052,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -2052,7 +2064,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>00100000111111000000000110110000</t>
+          <t>00100000111111000000011111100110</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -2062,7 +2074,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -2074,7 +2086,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>00100000111111000000011100111011</t>
+          <t>00100000111111000000010101000001</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -2084,19 +2096,19 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>00101110001110100000000000010001</t>
+          <t>00101110001110100000000000000011</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>00100000111111000000101101111111</t>
+          <t>00100000111111000000011010110101</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -2106,19 +2118,19 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>00101110001110100000000000010001</t>
+          <t>00101110001110100000000000000000</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>00100000111111000000001101011111</t>
+          <t>00100000111111000000001111101111</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -2128,19 +2140,19 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>00101110001110100000000000000000</t>
+          <t>00101110001110100000000000010011</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>00100000111111000000000000000111</t>
+          <t>00100000111111000000100101111010</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -2150,19 +2162,19 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>00101110001110100000000000000000</t>
+          <t>00101110001110100000000000010011</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>00100000111111000000100010000101</t>
+          <t>00100000111111000000011011100000</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -2172,7 +2184,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -2184,7 +2196,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>00100000111111000000011110001100</t>
+          <t>00100000111111000000011101011001</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -2194,19 +2206,19 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>00101110001110100000000000010011</t>
+          <t>00101110001110100000000000010101</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>00100000111111000000101010111110</t>
+          <t>00100000111111000000010100000101</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -2216,19 +2228,19 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>00101110001110100000000000010011</t>
+          <t>00101110001110100000000000000011</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>00100000111111000000011100101010</t>
+          <t>00100000111111000000100001001100</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -2238,19 +2250,19 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>00101110001110100000000000010011</t>
+          <t>00101110001110100000000000010101</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>00100000111111000000100111011001</t>
+          <t>00100000111111000000000101110100</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -2260,19 +2272,19 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>00101110001110100000000000010011</t>
+          <t>00101110001110100000000000000011</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>00100000111111000000011101011001</t>
+          <t>00100000111111000000011011110111</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -2282,19 +2294,19 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>00101110001110100000000000010011</t>
+          <t>00101110001110100000000000010110</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>00100000111111000000000000010010</t>
+          <t>00100000111111000000001100110101</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -2304,19 +2316,19 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>00101110001110100000000000010101</t>
+          <t>00101110001110100000000000010110</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>00100000111111000000011000000100</t>
+          <t>00100000111111000000011000001100</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -2326,19 +2338,19 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>00101110001110100000000000010101</t>
+          <t>00101110001110100000000000000101</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>00100000111111000000011101010010</t>
+          <t>00100000111111000000101001011101</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -2348,19 +2360,19 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>00101110001110100000000000010101</t>
+          <t>00101110001110100000000000000101</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>00100000111111000000011000010110</t>
+          <t>00100000111111000000000111000001</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -2377,12 +2389,12 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>00101110001110100000000000010110</t>
+          <t>00101110001110100000000000000101</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>00100000111111000000101111011010</t>
+          <t>00100000111111000000010000111000</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -2392,7 +2404,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -2404,7 +2416,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>00100000111111000000011010110010</t>
+          <t>00100000111111000000000011011001</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -2414,19 +2426,19 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>00101110001110100000000000010110</t>
+          <t>00101110001110100000000000000101</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>00100000111111000000000000010000</t>
+          <t>00100000111111000000000001101001</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -2436,7 +2448,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -2448,7 +2460,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>00100000111111000000100010000101</t>
+          <t>00100000111111000000010010100000</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -2458,7 +2470,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -2470,7 +2482,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>00100000111111000000010111001101</t>
+          <t>00100000111111000000001110001100</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -2480,7 +2492,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -2492,7 +2504,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>00100000111111000000000110000111</t>
+          <t>00100000111111000000000000010010</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -2502,19 +2514,19 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>00101110001110100000000000010110</t>
+          <t>00101110001110100000000000000101</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>00100000111111000000000111110001</t>
+          <t>00100000111111000000101010001110</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -2524,19 +2536,19 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>00101110001110100000000000010110</t>
+          <t>00101110001110100000000000000101</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>00100000111111000000101110111101</t>
+          <t>00100000111111000000100001111110</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -2546,19 +2558,19 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>00101110001110100000000000010110</t>
+          <t>00101110001110100000000000010111</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>00100000111111000000101000101101</t>
+          <t>00100000111111000000010110110100</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -2568,19 +2580,19 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>00101110001110100000000000010110</t>
+          <t>00101110001110100000000000010111</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>00100000111111000000011100110101</t>
+          <t>00100000111111000000100101001100</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -2590,19 +2602,19 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>00101110001110100000000000010111</t>
+          <t>00101110001110100000000000000101</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>00100000111111000000000100100001</t>
+          <t>00100000111111000000010110110000</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -2612,19 +2624,19 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>00101110001110100000000000010111</t>
+          <t>00101110001110100000000000011001</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>00100000111111000000011000001111</t>
+          <t>00100000111111000000000000010000</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -2634,19 +2646,19 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>00101110001110100000000000010111</t>
+          <t>00101110001110100000000000011010</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>00100000111111000000100010000101</t>
+          <t>00100000111111000000000111101100</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -2656,19 +2668,19 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>00101110001110100000000000010111</t>
+          <t>00101110001110100000000000011010</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>00100000111111000000001011000011</t>
+          <t>00100000111111000000101100001101</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -2678,19 +2690,19 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>00101110001110100000000000010111</t>
+          <t>00101110001110100000000000011010</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>00100000111111000000010000100111</t>
+          <t>00100000111111000000100101110110</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -2700,19 +2712,19 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>00101110001110100000000000010111</t>
+          <t>00101110001110100000000000011010</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>00100000111111000000011010110101</t>
+          <t>00100000111111000000000010110111</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -2722,19 +2734,19 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>00101110001110100000000000010111</t>
+          <t>00101110001110100000000000011010</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>00100000111111000000010101000001</t>
+          <t>00100000111111000000011000110101</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -2744,19 +2756,19 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>00101110001110100000000000010111</t>
+          <t>00101110001110100000000000011010</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>00100000111111000000100010101111</t>
+          <t>00100000111111000000011001000011</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -2766,19 +2778,19 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>00101110001110100000000000011001</t>
+          <t>00101110001110100000000000000101</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>00100000111111000000011101111011</t>
+          <t>00100000111111000000001110101100</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -2788,19 +2800,19 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>00101110001110100000000000011001</t>
+          <t>00101110001110100000000000000101</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>00100000111111000000001011011110</t>
+          <t>00100000111111000000011111101110</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -2810,19 +2822,19 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>00101110001110100000000000011001</t>
+          <t>00101110001110100000000000011010</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>00100000111111000000010100000101</t>
+          <t>00100000111111000000010111001101</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -2832,19 +2844,19 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>00101110001110100000000000011010</t>
+          <t>00101110001110100000000000000101</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>00100000111111000000000000000111</t>
+          <t>00100000111111000000011110001000</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -2861,12 +2873,12 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>00101110001110100000000000011010</t>
+          <t>00101110001110100000000000011011</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>00100000111111000000001010101001</t>
+          <t>00100000111111000000100111101010</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -2876,19 +2888,19 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>00101110001110100000000000011010</t>
+          <t>00101110001110100000000000011011</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>00100000111111000000001101011111</t>
+          <t>00100000111111000000101001111000</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -2898,19 +2910,19 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>00101110001110100000000000011010</t>
+          <t>00101110001110100000000000011011</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>00100000111111000000101010001111</t>
+          <t>00100000111111000000100110101001</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -2920,19 +2932,19 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>00101110001110100000000000011010</t>
+          <t>00101110001110100000000000011100</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>00100000111111000000100100010010</t>
+          <t>00100000111111000000101011000110</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -2942,19 +2954,19 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>00101110001110100000000000011010</t>
+          <t>00101110001110100000000000011100</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>00100000111111000000100110011010</t>
+          <t>00100000111111000000100010110101</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -2964,19 +2976,19 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>00101110001110100000000000011010</t>
+          <t>00101110001110100000000000011100</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>00100000111111000000000111101100</t>
+          <t>00100000111111000000100010000101</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -2986,19 +2998,19 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>00101110001110100000000000011010</t>
+          <t>00101110001110100000000000011100</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>00100000111111000000010001010011</t>
+          <t>00100000111111000000010100010110</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -3008,19 +3020,19 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>00101110001110100000000000011010</t>
+          <t>00101110001110100000000000011100</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>00100000111111000000001111011110</t>
+          <t>00100000111111000000010001001100</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -3030,19 +3042,19 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>00101110001110100000000000011011</t>
+          <t>00101110001110100000000000011101</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>00100000111111000000000101101100</t>
+          <t>00100000111111000000000110000111</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -3052,19 +3064,19 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>00101110001110100000000000011011</t>
+          <t>00101110001110100000000000000101</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>00100000111111000000000011011010</t>
+          <t>00100000111111000000100001010110</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -3081,12 +3093,12 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>00101110001110100000000000011011</t>
+          <t>00101110001110100000000000011101</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>00100000111111000000100111000011</t>
+          <t>00100000111111000000010111010100</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -3096,19 +3108,19 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>00101110001110100000000000011100</t>
+          <t>00101110001110100000000000011101</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>00100000111111000000000101101100</t>
+          <t>00100000111111000000000101011000</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -3118,19 +3130,19 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>00101110001110100000000000011100</t>
+          <t>00101110001110100000000000011101</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>00100000111111000000101100001100</t>
+          <t>00100000111111000000101100110011</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -3140,19 +3152,19 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>00101110001110100000000000011100</t>
+          <t>00101110001110100000000000011101</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>00100000111111000000011111101110</t>
+          <t>00100000111111000000001010011111</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -3162,19 +3174,19 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>00101110001110100000000000011100</t>
+          <t>00101110001110100000000000011101</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>00100000111111000000001010100111</t>
+          <t>00100000111111000000010111100110</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -3184,19 +3196,19 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>00101110001110100000000000011100</t>
+          <t>00101110001110100000000000011101</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>00100000111111000000000111110010</t>
+          <t>00100000111111000000010100110100</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -3206,19 +3218,19 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>00101110001110100000000000011100</t>
+          <t>00101110001110100000000000011101</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>00100000111111000000000010011101</t>
+          <t>00100000111111000000100100001001</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -3228,19 +3240,19 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>00101110001110100000000000011100</t>
+          <t>00101110001110100000000000000110</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>00100000111111000000100011110010</t>
+          <t>00100000111111000000010010110001</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -3250,19 +3262,19 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>00101110001110100000000000011100</t>
+          <t>00101110001110100000000000011110</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>00100000111111000000011000110101</t>
+          <t>00100000111111000000001010101010</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -3272,19 +3284,19 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>00101110001110100000000000011101</t>
+          <t>00101110001110100000000000011110</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>00100000111111000000101101010010</t>
+          <t>00100000111111000000011011110011</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -3294,19 +3306,19 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>00101110001110100000000000011101</t>
+          <t>00101110001110100000000000000110</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>00100000111111000000010101010011</t>
+          <t>00100000111111000000011100010101</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -3316,19 +3328,19 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>00101110001110100000000000011101</t>
+          <t>00101110001110100000000000000110</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>00100000111111000000010111001101</t>
+          <t>00100000111111000000000001001110</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -3338,19 +3350,19 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>00101110001110100000000000011101</t>
+          <t>00101110001110100000000000000110</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>00100000111111000000001111101111</t>
+          <t>00100000111111000000100110000110</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -3360,19 +3372,19 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>00101110001110100000000000011101</t>
+          <t>00101110001110100000000000011110</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>00100000111111000000010000111101</t>
+          <t>00100000111111000000100101101111</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -3382,19 +3394,19 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>00101110001110100000000000011101</t>
+          <t>00101110001110100000000000000110</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>00100000111111000000010000111000</t>
+          <t>00100000111111000000010101100000</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -3404,19 +3416,19 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>00101110001110100000000000011110</t>
+          <t>00101110001110100000000000000110</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>00100000111111000000101000101001</t>
+          <t>00100000111111000000101001011010</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -3426,19 +3438,19 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>00101110001110100000000000011110</t>
+          <t>00101110001110100000000000100000</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>00100000111111000000101000010101</t>
+          <t>00100000111111000000100111011111</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -3448,19 +3460,19 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>00101110001110100000000000011110</t>
+          <t>00101110001110100000000000100000</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>00100000111111000000100101101111</t>
+          <t>00100000111111000000000011010010</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -3470,19 +3482,19 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>00101110001110100000000000011110</t>
+          <t>00101110001110100000000000100000</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>00100000111111000000001111011110</t>
+          <t>00100000111111000000010110001010</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -3492,19 +3504,19 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>00101110001110100000000000011110</t>
+          <t>00101110001110100000000000100000</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>00100000111111000000000111101100</t>
+          <t>00100000111111000000011101111011</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -3514,19 +3526,19 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>00101110001110100000000000001101</t>
+          <t>00101110001110100000000000100000</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>00100000111111000000000001001110</t>
+          <t>00100000111111000000011010110010</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -3536,19 +3548,19 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>00101110001110100000000000001101</t>
+          <t>00101110001110100000000000100000</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>00100000111111000000011111101110</t>
+          <t>00100000111111000000011000111110</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -3558,19 +3570,19 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>00101110001110100000000000001101</t>
+          <t>00101110001110100000000000100000</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>00100000111111000000001010100111</t>
+          <t>00100000111111000000000000000111</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -3580,19 +3592,19 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>00101110001110100000000000001101</t>
+          <t>00101110001110100000000000100000</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>00100000111111000000011110010100</t>
+          <t>00100000111111000000011100001010</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -3602,19 +3614,19 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>00101110001110100000000000001101</t>
+          <t>00101110001110100000000000100001</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>00100000111111000000011011011111</t>
+          <t>00100000111111000000100100000010</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -3624,14 +3636,14 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>00101110001110100000000000011111</t>
+          <t>00101110001110100000000000100001</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -3646,19 +3658,19 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>00101110001110100000000000011111</t>
+          <t>00101110001110100000000000100001</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>00100000111111000000100000110111</t>
+          <t>00100000111111000000001101011111</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -3668,19 +3680,19 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>00101110001110100000000000011111</t>
+          <t>00101110001110100000000000100001</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>00100000111111000000011000010110</t>
+          <t>00100000111111000000001011001101</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -3690,19 +3702,19 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>00101110001110100000000000011111</t>
+          <t>00101110001110100000000000100001</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>00100000111111000000001001111001</t>
+          <t>00100000111111000000001011000011</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -3712,19 +3724,19 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>00101110001110100000000000011111</t>
+          <t>00101110001110100000000000100001</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>00100000111111000000000000010000</t>
+          <t>00100000111111000000001011111101</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -3734,19 +3746,19 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>00101110001110100000000000011111</t>
+          <t>00101110001110100000000000100001</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>00100000111111000000010011010011</t>
+          <t>00100000111111000000101110101111</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -3756,19 +3768,19 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>00101110001110100000000000011111</t>
+          <t>00101110001110100000000000100001</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>00100000111111000000000100100001</t>
+          <t>00100000111111000000101101110001</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -3778,19 +3790,19 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>00101110001110100000000000011111</t>
+          <t>00101110001110100000000000100001</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>00100000111111000000011100100000</t>
+          <t>00100000111111000000000011010011</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -3800,19 +3812,19 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>00101110001110100000000000011111</t>
+          <t>00101110001110100000000000000111</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>00100000111111000000000000010010</t>
+          <t>00100000111111000000000100101101</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -3822,19 +3834,19 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>00101110001110100000000000011111</t>
+          <t>00101110001110100000000000100011</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>00100000111111000000000110110000</t>
+          <t>00100000111111000000010110000101</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -3844,19 +3856,19 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>00101110001110100000000000100000</t>
+          <t>00101110001110100000000000100100</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>00100000111111000000100010110101</t>
+          <t>00100000111111000000000010100100</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -3866,19 +3878,19 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>00101110001110100000000000100000</t>
+          <t>00101110001110100000000000100100</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>00100000111111000000010010110001</t>
+          <t>00100000111111000000011111100001</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -3888,19 +3900,19 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>00101110001110100000000000100000</t>
+          <t>00101110001110100000000000100100</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>00100000111111000000011000010110</t>
+          <t>00100000111111000000011100111011</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -3910,19 +3922,19 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>00101110001110100000000000100000</t>
+          <t>00101110001110100000000000100100</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>00100000111111000000011100110101</t>
+          <t>00100000111111000000011001011100</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -3932,19 +3944,19 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>00101110001110100000000000100000</t>
+          <t>00101110001110100000000000100100</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>00100000111111000000010111001101</t>
+          <t>00100000111111000000010101111101</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -3954,19 +3966,19 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>00101110001110100000000000100001</t>
+          <t>00101110001110100000000000000101</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>00100000111111000000000000010000</t>
+          <t>00100000111111000000000110110110</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -3983,12 +3995,12 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>00101110001110100000000000100001</t>
+          <t>00101110001110100000000000100010</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>00100000111111000000010011111111</t>
+          <t>00100000111111000000100110011011</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -3998,19 +4010,19 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>00101110001110100000000000100001</t>
+          <t>00101110001110100000000000000111</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>00100000111111000000001011001101</t>
+          <t>00100000111111000000001111111101</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -4020,19 +4032,19 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>00101110001110100000000000100001</t>
+          <t>00101110001110100000000000000111</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>00100000111111000000000101101100</t>
+          <t>00100000111111000000000100010101</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -4042,19 +4054,19 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>00101110001110100000000000100001</t>
+          <t>00101110001110100000000000000111</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>00100000111111000000101110101111</t>
+          <t>00100000111111000000000111111001</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -4064,19 +4076,19 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>00101110001110100000000000100011</t>
+          <t>00101110001110100000000000000111</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>00100000111111000000100011001110</t>
+          <t>00100000111111000000100101110101</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -4093,12 +4105,12 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>00101110001110100000000000100011</t>
+          <t>00101110001110100000000000000111</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>00100000111111000000000101000100</t>
+          <t>00100000111111000000011111011001</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -4108,19 +4120,19 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>00101110001110100000000000100011</t>
+          <t>00101110001110100000000000000111</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>00100000111111000000011101001101</t>
+          <t>00100000111111000000100000111001</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -4130,19 +4142,19 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>00101110001110100000000000100011</t>
+          <t>00101110001110100000000000000111</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>00100000111111000000011100101010</t>
+          <t>00100000111111000000100000010101</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -4152,19 +4164,19 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>00101110001110100000000000100100</t>
+          <t>00101110001110100000000000000111</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>00100000111111000000001010011111</t>
+          <t>00100000111111000000001100110011</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -4174,19 +4186,19 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>00101110001110100000000000100100</t>
+          <t>00101110001110100000000000001010</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>00100000111111000000010101100000</t>
+          <t>00100000111111000000100000010111</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -4196,19 +4208,19 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>00101110001110100000000000100100</t>
+          <t>00101110001110100000000000001010</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>00100000111111000000011000010110</t>
+          <t>00100000111111000000100111110001</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -4218,19 +4230,19 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>00101110001110100000000000100100</t>
+          <t>00101110001110100000000000001010</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>00100000111111000000000011011001</t>
+          <t>00100000111111000000101110111101</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -4240,19 +4252,19 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>00101110001110100000000000100100</t>
+          <t>00101110001110100000000000001010</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>00100000111111000000001110110000</t>
+          <t>00100000111111000000001110001110</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -4262,19 +4274,19 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>00101110001110100000000000100010</t>
+          <t>00101110001110100000000000001010</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>00100000111111000000000001100011</t>
+          <t>00100000111111000000000111111011</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -4284,19 +4296,19 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>00101110001110100000000000100010</t>
+          <t>00101110001110100000000000000111</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>00100000111111000000000011011001</t>
+          <t>00100000111111000000000101100011</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -4313,12 +4325,12 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>00101110001110100000000000100010</t>
+          <t>00101110001110100000000000000111</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>00100000111111000000010100010110</t>
+          <t>00100000111111000000100110111100</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -4335,12 +4347,12 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>00101110001110100000000000100010</t>
+          <t>00101110001110100000000000000111</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>00100000111111000000010110001101</t>
+          <t>00100000111111000000000111111010</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -4357,12 +4369,12 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>00101110001110100000000000100010</t>
+          <t>00101110001110100000000000001010</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>00100000111111000000011111011111</t>
+          <t>00100000111111000000001010100111</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -4372,19 +4384,19 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>00101110001110100000000000100010</t>
+          <t>00101110001110100000000000001011</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>00100000111111000000011000001000</t>
+          <t>00100000111111000000100100100101</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -4394,178 +4406,178 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>00000000000000000000000010110011</t>
+          <t>00101110001110100000000000001011</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100000111111000000000000110000</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100001011110100000000010110100</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>00000000000000000000000010100000</t>
+          <t>00101110001110100000000000001011</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100000111111000000001010010011</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100001011110100000000010110101</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>00000000000000000000000011110000</t>
+          <t>00101110001110100000000000001011</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100000111111000000011111111101</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100001011110100000000010110110</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>00000000000000000000000010110110</t>
+          <t>00101110001110100000000000001100</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100000111111000000100001011110</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100001011110100000000010110111</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>00000000000000000000000010100011</t>
+          <t>00101110001110100000000000001100</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100000111111000000011111101000</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100001011110100000000010111000</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>00000000000000000000000011100100</t>
+          <t>00101110001110100000000000001100</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100000111111000000101101100100</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100001011110100000000010111001</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>00000000000000000000000010111001</t>
+          <t>00101110001110100000000000001100</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100000111111000000011101001101</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100001011110100000000010111010</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>00000000000000000000000010011101</t>
+          <t>00101110001110100000000000000111</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100000111111000000101110101011</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100001011110100000000010111011</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -4577,83 +4589,83 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>00000000000000000000000010011110</t>
+          <t>00101110001110100000000000001100</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100000111111000000000110110000</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100001011110100000000010111100</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>00000000000000000000000010110000</t>
+          <t>00101110001110100000000000001111</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100000111111000000100011100010</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100001011110100000000010111101</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>00000000000000000000000011010111</t>
+          <t>00101110001110100000000000001111</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100000111111000000001000010000</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100001011110100000000010111110</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>00000000000000000000000010011111</t>
+          <t>00101110001110100000000000000111</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100000111111000000011111000110</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100001011110100000000010111111</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -4665,83 +4677,83 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>00000000000000000000000001101101</t>
+          <t>00101110001110100000000000001111</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100000111111000000000101000000</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100001011110100000000011000000</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>00000000000000000000000011010100</t>
+          <t>00101110001110100000000000001111</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100000111111000000011100101010</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100001011110100000000011000001</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>00000000000000000000000011100111</t>
+          <t>00101110001110100000000000001111</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100000111111000000010011100111</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100001011110100000000011000010</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>00000000000000000000000000111000</t>
+          <t>00101110001110100000000000001010</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100000111111000000011111011111</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100001011110100000000011000011</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -4753,83 +4765,83 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>00000000000000000000000000010001</t>
+          <t>00101110001110100000000000001111</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100000111111000000101101110100</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100001011110100000000011000100</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>00000000000000000000000010101110</t>
+          <t>00101110001110100000000000001111</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100000111111000000000111110001</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100001011110100000000011000101</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>00000000000000000000000010100100</t>
+          <t>00101110001110100000000000010001</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100000111111000000100011011110</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100001011110100000000011000110</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>00000000000000000000000010100110</t>
+          <t>00101110001110100000000000001010</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100000111111000000001110010110</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100001011110100000000011000111</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -4841,17 +4853,17 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>00000000000000000000000000100001</t>
+          <t>00101110001110100000000000001010</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100000111111000000001101100000</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100001011110100000000011001000</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -4863,237 +4875,237 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>00000000000000000000000001100001</t>
+          <t>00101110001110100000000000010101</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100000111111000000011010010110</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100001011110100000000011001001</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>00000000000000000000000011001110</t>
+          <t>00101110001110100000000000010101</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100000111111000000000000001110</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100001011110100000000011001010</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>00000000000000000000000010100101</t>
+          <t>00101110001110100000000000010101</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100000111111000000100011110101</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100001011110100000000011001011</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>00000000000000000000000010101001</t>
+          <t>00101110001110100000000000010101</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100000111111000000101000101101</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100001011110100000000011001100</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>00000000000000000000000010010110</t>
+          <t>00101110001110100000000000010101</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100000111111000000000010011101</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100001011110100000000011001101</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>00000000000000000000000010001111</t>
+          <t>00101110001110100000000000010101</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100000111111000000000111111101</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100001011110100000000011001110</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>00000000000000000000000010000100</t>
+          <t>00101110001110100000000000010101</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100000111111000000001101001010</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100001011110100000000011001111</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>00000000000000000000000011100010</t>
+          <t>00101110001110100000000000010101</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100000111111000000001100011010</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100001011110100000000011010000</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>00000000000000000000000001000001</t>
+          <t>00101110001110100000000000010101</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100000111111000000001001111110</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100001011110100000000011010001</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>00000000000000000000000001011110</t>
+          <t>00101110001110100000000000010101</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100000111111000000000000001001</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100001011110100000000011010010</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>00000000000000000000000010111100</t>
+          <t>00101110001110100000000000001010</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100000111111000000000000011110</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100001011110100000000011010011</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -5105,17 +5117,17 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>00000000000000000000000010011100</t>
+          <t>00101110001110100000000000001111</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100000111111000000001110110110</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100001011110100000000011010100</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -5127,61 +5139,61 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>00000000000000000000000010010101</t>
+          <t>00101110001110100000000000010110</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100000111111000000101011100110</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100001011110100000000011010101</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>00000000000000000000000001100100</t>
+          <t>00101110001110100000000000010110</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100000111111000000010010011001</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100001011110100000000011010110</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>00000000000000000000000000101111</t>
+          <t>00101110001110100000000000001111</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100000111111000000100110011010</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100001011110100000000011010111</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -5193,39 +5205,39 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>00000000000000000000000011011011</t>
+          <t>00101110001110100000000000010110</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100000111111000000001010010010</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100001011110100000000011011000</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>00000000000000000000000001000110</t>
+          <t>00101110001110100000000000001111</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100000111111000000011100101011</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100001011110100000000011011001</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -5237,61 +5249,61 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>00000000000000000000000000011101</t>
+          <t>00101110001110100000000000010110</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100000111111000000101000101001</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100001011110100000000011011010</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>00000000000000000000000011101110</t>
+          <t>00101110001110100000000000010110</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100000111111000000010010001001</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100001011110100000000011011011</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>00000000000000000000000010111101</t>
+          <t>00101110001110100000000000001111</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100000111111000000011001101101</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100001011110100000000011011100</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -5303,17 +5315,17 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>00000000000000000000000011100101</t>
+          <t>00101110001110100000000000001111</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100000111111000000011010001100</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100001011110100000000011011101</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -5325,83 +5337,83 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>00000000000000000000000010011000</t>
+          <t>00101110001110100000000000010111</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100000111111000000101011111100</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100001011110100000000011011110</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000001</t>
+          <t>00101110001110100000000000010111</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100000111111000000011010011110</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100001011110100000000011011111</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>00000000000000000000000011000010</t>
+          <t>00101110001110100000000000010111</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100000111111000000100111011001</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100001011110100000000011100000</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>00000000000000000000000011000110</t>
+          <t>00101110001110100000000000010001</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100000111111000000100101110101</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100001011110100000000011100001</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -5413,281 +5425,281 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>00000000000000000000000011001000</t>
+          <t>00101110001110100000000000011001</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100000111111000000011100101110</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100001011110100000000011100010</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>00000000000000000000000010100010</t>
+          <t>00101110001110100000000000011001</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100000111111000000110110001101</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100001011110100000000011100011</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>00000000000000000000000010110111</t>
+          <t>00101110001110100000000000011001</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100000111111000000100111110110</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100001011110100000000011100100</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>00000000000000000000000011001100</t>
+          <t>00101110001110100000000000011001</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100000111111000000010101110011</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100001011110100000000011100101</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000010</t>
+          <t>00101110001110100000000000011001</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100000111111000000000010010001</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100001011110100000000011100110</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>00000000000000000000000000100111</t>
+          <t>00101110001110100000000000011001</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100000111111000000000101010100</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100001011110100000000011100111</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>00000000000000000000000011001010</t>
+          <t>00101110001110100000000000011001</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100000111111000000101111110111</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100001011110100000000011101000</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>00000000000000000000000011011111</t>
+          <t>00101110001110100000000000011001</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100000111111000000111001010110</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100001011110100000000011101001</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>00000000000000000000000000001101</t>
+          <t>00101110001110100000000000011001</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100000111111000000100000001011</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100001011110100000000011101010</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>00000000000000000000000011110001</t>
+          <t>00101110001110100000000000011001</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100000111111000000101010000001</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100001011110100000000011101011</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>00000000000000000000000000011001</t>
+          <t>00101110001110100000000000011010</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100000111111000000011010111111</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100001011110100000000011101100</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>00000000000000000000000001100000</t>
+          <t>00101110001110100000000000011010</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100000111111000000000010010000</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100001011110100000000011101101</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>00000000000000000000000011011101</t>
+          <t>00101110001110100000000000010001</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100000111111000000100110011010</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100001011110100000000011101110</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -5699,83 +5711,83 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>00000000000000000000000001000100</t>
+          <t>00101110001110100000000000011010</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100000111111000000000000110111</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100001011110100000000011101111</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>00000000000000000000000010110100</t>
+          <t>00101110001110100000000000011011</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100000111111000000010110110111</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100001011110100000000011110000</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>00000000000000000000000011101001</t>
+          <t>00101110001110100000000000011011</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100000111111000000100100000110</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100001011110100000000011110001</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>00000000000000000000000010001010</t>
+          <t>00101110001110100000000000010001</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100000111111000000000000011110</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100001011110100000000011110010</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
@@ -5787,215 +5799,215 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>00000000000000000000000011010000</t>
+          <t>00101110001110100000000000011011</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100000111111000000101000010010</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100001011110100000000011110011</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>00000000000000000000000001011001</t>
+          <t>00101110001110100000000000011100</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100000111111000000001001010000</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100001011110100000000011110100</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>00000000000000000000000010010000</t>
+          <t>00101110001110100000000000011100</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100000111111000000011000001000</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100001011110100000000011110101</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>00000000000000000000000001011000</t>
+          <t>00101110001110100000000000011101</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100000111111000000000010111000</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100001011110100000000011110110</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>00000000000000000000000001000101</t>
+          <t>00101110001110100000000000011101</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100000111111000000111000111111</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100001011110100000000011110111</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>00000000000000000000000011110111</t>
+          <t>00101110001110100000000000011101</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100000111111000000100101010011</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100001011110100000000011111000</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>00000000000000000000000011111000</t>
+          <t>00101110001110100000000000011101</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100000111111000000110000010100</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100001011110100000000011111001</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>00000000000000000000000011111001</t>
+          <t>00101110001110100000000000011101</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100000111111000000100010001010</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100001011110100000000011111010</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>00000000000000000000000011111010</t>
+          <t>00101110001110100000000000011101</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100000111111000000000010111101</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100001011110100000000011111011</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>00000000000000000000000011111011</t>
+          <t>00101110001110100000000000010101</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100000111111000000001110110000</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100001011110100000000011111100</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
@@ -6007,61 +6019,61 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>00000000000000000000000011111100</t>
+          <t>00101110001110100000000000011110</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100000111111000000000001001111</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100001011110100000000011111101</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>00000000000000000000000011111101</t>
+          <t>00101110001110100000000000011110</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100000111111000000101100000011</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100001011110100000000011111110</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>00000000000000000000000011111110</t>
+          <t>00101110001110100000000000010110</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100000111111000000101111011000</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100001011110100000000011111111</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
@@ -6073,39 +6085,39 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>00000000000000000000000011111111</t>
+          <t>00101110001110100000000000011110</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100000111111000000000001010110</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100001011110100000000100000000</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>00000000000000000000000100000000</t>
+          <t>00101110001110100000000000010110</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100000111111000000011000101111</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100001011110100000000100000001</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
@@ -6117,523 +6129,523 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>00000000000000000000000100000001</t>
+          <t>00101110001110100000000000011110</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100000111111000000101000000011</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100001011110100000000100000010</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>00000000000000000000000100000010</t>
+          <t>00101110001110100000000000011110</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100000111111000000101110111000</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100001011110100000000100000011</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>00000000000000000000000100000011</t>
+          <t>00101110001110100000000000011110</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100000111111000000000101100100</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100001011110100000000100000100</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>00000000000000000000000100000100</t>
+          <t>00101110001110100000000000011110</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100000111111000000000001110111</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100001011110100000000100000101</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>00000000000000000000000100000101</t>
+          <t>00101110001110100000000000011111</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100000111111000000000101001000</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100001011110100000000100000110</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>00000000000000000000000100000110</t>
+          <t>00101110001110100000000000011111</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100000111111000000010011101100</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100001011110100000000100000111</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>100000111</t>
+          <t>00101110001110100000000000100000</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100000111111000000101101001111</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100001011110100000000100001000</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>00000000000000000000000010110101</t>
+          <t>00101110001110100000000000100000</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100000111111000000101101111100</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100001011110100000000100001001</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>00000000000000000000000100001011</t>
+          <t>00101110001110100000000000100000</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100000111111000000011100110101</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100001011110100000000100001010</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>00000000000000000000000100001100</t>
+          <t>00101110001110100000000000100000</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100000111111000000001010010000</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100001011110100000000100001011</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>00000000000000000000000100001101</t>
+          <t>00101110001110100000000000100000</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100000111111000000000010011111</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100001011110100000000100001100</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>00000000000000000000000100001110</t>
+          <t>00101110001110100000000000100000</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100000111111000000010111011011</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100001011110100000000100001101</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>00000000000000000000000100001111</t>
+          <t>00101110001110100000000000100000</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100000111111000000101000010101</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100001011110100000000100001110</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>00000000000000000000000100010000</t>
+          <t>00101110001110100000000000100000</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100000111111000000001111010101</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100001011110100000000100001111</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>00000000000000000000000100010001</t>
+          <t>00101110001110100000000000100001</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100000111111000000001110000110</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100001011110100000000100010000</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>00000000000000000000000100010010</t>
+          <t>00101110001110100000000000100001</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100000111111000000100101000111</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100001011110100000000100010001</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>00000000000000000000000100010011</t>
+          <t>00101110001110100000000000100001</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100000111111000000000001011111</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100001011110100000000100010010</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>00000000000000000000000100010100</t>
+          <t>00101110001110100000000000100011</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100000111111000000101100110101</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100001011110100000000100010011</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>00000000000000000000000100010101</t>
+          <t>00101110001110100000000000100011</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100000111111000000101100111101</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100001011110100000000100010100</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>00000000000000000000000100010110</t>
+          <t>00101110001110100000000000100011</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100000111111000000010000000000</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100001011110100000000100010101</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>00000000000000000000000100010111</t>
+          <t>00101110001110100000000000100011</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100000111111000000001110101011</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100001011110100000000100010110</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>00000000000000000000000100011000</t>
+          <t>00101110001110100000000000100011</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100000111111000000100000111111</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100001011110100000000100010111</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>00000000000000000000000100011001</t>
+          <t>00101110001110100000000000100100</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100000111111000000011111011011</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100001011110100000000100011000</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>00000000000000000000000100011010</t>
+          <t>00101110001110100000000000010110</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100000111111000000010101110101</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100001011110100000000100011001</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
@@ -6645,17 +6657,17 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>00000000000000000000000100011011</t>
+          <t>00101110001110100000000000010110</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100000111111000000010110011110</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100001011110100000000100011010</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
@@ -6667,39 +6679,39 @@
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>00000000000000000000000100011100</t>
+          <t>00101110001110100000000000100100</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100000111111000000011001111011</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100001011110100000000100011011</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>00000000000000000000000100011101</t>
+          <t>00101110001110100000000000010110</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100000111111000000100010100001</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100001011110100000000100011100</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
@@ -6711,259 +6723,259 @@
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>00000000000000000000000100011110</t>
+          <t>00101110001110100000000000100100</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100000111111000000101011011111</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100001011110100000000100011101</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>00000000000000000000000100011111</t>
+          <t>00101110001110100000000000100100</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100000111111000000110000111011</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100001011110100000000100011110</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>00000000000000000000000100100000</t>
+          <t>00101110001110100000000000100100</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100000111111000000100100011010</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100001011110100000000100011111</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>00000000000000000000000100100001</t>
+          <t>00101110001110100000000000100100</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100000111111000000110000011010</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100001011110100000000100100000</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>00000000000000000000000100100010</t>
+          <t>00101110001110100000000000100100</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100000111111000000000110000110</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100001011110100000000100100001</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>00000000000000000000000100100011</t>
+          <t>00101110001110100000000000100010</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100000111111000000001010110011</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100001011110100000000100100010</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>00000000000000000000000100100100</t>
+          <t>00101110001110100000000000100010</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100000111111000000100110001010</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100001011110100000000100100011</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>00000000000000000000000100100101</t>
+          <t>00101110001110100000000000100010</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100000111111000000001110010100</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100001011110100000000100100100</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>00000000000000000000000100100110</t>
+          <t>00101110001110100000000000100010</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100000111111000000001000010111</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100001011110100000000100100101</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>00000000000000000000000100100111</t>
+          <t>00101110001110100000000000100010</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100000111111000000100001110001</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100001011110100000000100100110</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>00000000000000000000000100101000</t>
+          <t>00101110001110100000000000100010</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100000111111000000001110100011</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100001011110100000000100100111</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>00000000000000000000000100101001</t>
+          <t>00101110001110100000000000010110</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100000111111000000010000100111</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100001011110100000000100101000</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
@@ -6975,17 +6987,17 @@
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>00000000000000000000000100101010</t>
+          <t>00101110001110100000000000010110</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100000111111000000101011010110</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100001011110100000000100101001</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
@@ -6997,61 +7009,61 @@
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>00000000000000000000000100101011</t>
+          <t>00101110001110100000000000011111</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100000111111000000101001100010</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100001011110100000000100101010</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>00000000000000000000000100101100</t>
+          <t>00101110001110100000000000011111</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100000111111000000101011101010</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100001011110100000000100101011</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>00000000000000000000000100101101</t>
+          <t>00101110001110100000000000010110</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100000111111000000101110001111</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100001011110100000000100101100</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
@@ -7063,17 +7075,17 @@
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>00000000000000000000000100101110</t>
+          <t>00101110001110100000000000010110</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100000111111000000001000010011</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100001011110100000000100101101</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
@@ -7085,17 +7097,17 @@
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>00000000000000000000000100101111</t>
+          <t>00101110001110100000000000010110</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100000111111000000011101000000</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100001011110100000000100101110</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
@@ -7107,17 +7119,17 @@
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>00000000000000000000000100110000</t>
+          <t>00101110001110100000000000010111</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100000111111000000100110111000</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100001011110100000000100101111</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
@@ -7129,17 +7141,17 @@
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>00000000000000000000000100110001</t>
+          <t>00101110001110100000000000010111</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100000111111000000010110010010</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100001011110100000000100110000</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
@@ -7151,17 +7163,17 @@
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>00000000000000000000000100110010</t>
+          <t>00101110001110100000000000011010</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100000111111000000011000100111</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100001011110100000000100110001</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
@@ -7173,17 +7185,17 @@
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>00000000000000000000000100110011</t>
+          <t>00101110001110100000000000011110</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100000111111000000101110101011</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100001011110100000000100110010</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
@@ -7195,17 +7207,17 @@
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>00000000000000000000000100110100</t>
+          <t>00101110001110100000000000011110</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100000111111000000010010101110</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100001011110100000000100110011</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
@@ -7217,17 +7229,17 @@
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>00000000000000000000000100110101</t>
+          <t>00101110001110100000000000011110</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100000111111000000000111000001</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100001011110100000000100110100</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
@@ -7239,17 +7251,17 @@
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>00000000000000000000000100110110</t>
+          <t>00101110001110100000000000011110</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100000111111000000011111000110</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100001011110100000000100110101</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
@@ -7261,17 +7273,17 @@
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>00000000000000000000000100110111</t>
+          <t>00101110001110100000000000011110</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100000111111000000100001010110</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100001011110100000000100110110</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
@@ -7283,17 +7295,17 @@
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>00000000000000000000000100111000</t>
+          <t>00101110001110100000000000011110</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100000111111000000101100110111</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100001011110100000000100110111</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
@@ -7305,17 +7317,17 @@
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>00000000000000000000000100111001</t>
+          <t>00101110001110100000000000100100</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100000111111000000010110000011</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100001011110100000000100111000</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
@@ -7327,17 +7339,17 @@
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>00000000000000000000000100111010</t>
+          <t>00101110001110100000000000100100</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100000111111000000000011011110</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100001011110100000000100111001</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
@@ -7349,17 +7361,17 @@
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>00000000000000000000000100111011</t>
+          <t>00101110001110100000000000100100</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100000111111000000010010000110</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>00000000000000000000000000000000</t>
+          <t>00100001011110100000000100111010</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">

--- a/Files/Madden26/IE/Season2/FreeAgency/Output/ContractOffer.xlsx
+++ b/Files/Madden26/IE/Season2/FreeAgency/Output/ContractOffer.xlsx
@@ -458,7 +458,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>00100000111111000000000111100100</t>
+          <t>00100000111111000000100101111010</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -468,7 +468,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
@@ -480,7 +480,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>00100000111111000000100101000010</t>
+          <t>00100000111111000000001110110111</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -490,7 +490,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>00100000111111000000000011011010</t>
+          <t>00100000111111000000000110110000</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -512,19 +512,19 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>00101110001110100000000000000001</t>
+          <t>00101110001110100000000000000010</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>00100000111111000000100011001001</t>
+          <t>00100000111111000000010111001110</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -534,19 +534,19 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>00101110001110100000000000000001</t>
+          <t>00101110001110100000000000000010</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>00100000111111000000000111010111</t>
+          <t>00100000111111000000101000101101</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -556,19 +556,19 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>00101110001110100000000000000001</t>
+          <t>00101110001110100000000000000010</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>00100000111111000000100111100100</t>
+          <t>00100000111111000000101010000001</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -578,19 +578,19 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>00101110001110100000000000000001</t>
+          <t>00101110001110100000000000000010</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>00100000111111000000011101000100</t>
+          <t>00100000111111000000101011101010</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -600,7 +600,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
@@ -612,7 +612,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>00100000111111000000010011111111</t>
+          <t>00100000111111000000010101000001</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -622,19 +622,19 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>00101110001110100000000000000001</t>
+          <t>00101110001110100000000000000011</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>00100000111111000000000110100100</t>
+          <t>00100000111111000000100000010011</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -644,19 +644,19 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>00101110001110100000000000000001</t>
+          <t>00101110001110100000000000000011</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>00100000111111000000000100011011</t>
+          <t>00100000111111000000101010000100</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -666,19 +666,19 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>00101110001110100000000000000010</t>
+          <t>00101110001110100000000000000011</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>00100000111111000000001111101001</t>
+          <t>00100000111111000000000000000110</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -688,19 +688,19 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>00101110001110100000000000000010</t>
+          <t>00101110001110100000000000000011</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>00100000111111000000011110110111</t>
+          <t>00100000111111000000010100110100</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -710,19 +710,19 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>00101110001110100000000000000010</t>
+          <t>00101110001110100000000000000011</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>00100000111111000000001011001011</t>
+          <t>00100000111111000000011111011001</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -732,7 +732,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
@@ -744,7 +744,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>00100000111111000000101000001110</t>
+          <t>00100000111111000000001011001101</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -754,7 +754,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
@@ -766,7 +766,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>00100000111111000000101010000100</t>
+          <t>00100000111111000000011011011111</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -776,19 +776,19 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>00101110001110100000000000000011</t>
+          <t>00101110001110100000000000000100</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>00100000111111000000101001010111</t>
+          <t>00100000111111000000001011001011</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -798,19 +798,19 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>00101110001110100000000000000011</t>
+          <t>00101110001110100000000000000100</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>00100000111111000000100110011110</t>
+          <t>00100000111111000000001010100111</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -820,19 +820,19 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>00101110001110100000000000000011</t>
+          <t>00101110001110100000000000000100</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>00100000111111000000100011001110</t>
+          <t>00100000111111000000101001100010</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -842,19 +842,19 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>00101110001110100000000000000011</t>
+          <t>00101110001110100000000000000100</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>00100000111111000000101111011010</t>
+          <t>00100000111111000000101110101011</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -864,19 +864,19 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>00101110001110100000000000000010</t>
+          <t>00101110001110100000000000000101</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>00100000111111000000101010010101</t>
+          <t>00100000111111000000001100110101</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -893,12 +893,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>00101110001110100000000000000100</t>
+          <t>00101110001110100000000000000101</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>00100000111111000000100010001111</t>
+          <t>00100000111111000000011000010110</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -908,19 +908,19 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>00101110001110100000000000000100</t>
+          <t>00101110001110100000000000000101</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>00100000111111000000011011101110</t>
+          <t>00100000111111000000010110000101</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -930,19 +930,19 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>00101110001110100000000000000100</t>
+          <t>00101110001110100000000000000101</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>00100000111111000000000001100011</t>
+          <t>00100000111111000000101001011101</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -952,19 +952,19 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>00101110001110100000000000000100</t>
+          <t>00101110001110100000000000000101</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>00100000111111000000001101000110</t>
+          <t>00100000111111000000011001000101</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -974,19 +974,19 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>00101110001110100000000000000100</t>
+          <t>00101110001110100000000000000101</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>00100000111111000000011010100000</t>
+          <t>00100000111111000000100001011110</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -996,19 +996,19 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>00101110001110100000000000000100</t>
+          <t>00101110001110100000000000000101</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>00100000111111000000011010111110</t>
+          <t>00100000111111000000101101111111</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1018,19 +1018,19 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>00101110001110100000000000000001</t>
+          <t>00101110001110100000000000000101</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>00100000111111000000011110010110</t>
+          <t>00100000111111000000010000111000</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1040,19 +1040,19 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>00101110001110100000000000000001</t>
+          <t>00101110001110100000000000000101</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>00100000111111000000000100100001</t>
+          <t>00100000111111000000000110100100</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>00100000111111000000001011110000</t>
+          <t>00100000111111000000000101101100</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1084,19 +1084,19 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>00101110001110100000000000000101</t>
+          <t>00101110001110100000000000000110</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>00100000111111000000000000101011</t>
+          <t>00100000111111000000011011011111</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1106,19 +1106,19 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>00101110001110100000000000000001</t>
+          <t>00101110001110100000000000000110</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>00100000111111000000011111001101</t>
+          <t>00100000111111000000101010000001</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1128,19 +1128,19 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>00101110001110100000000000000101</t>
+          <t>00101110001110100000000000000110</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>00100000111111000000101011110100</t>
+          <t>00100000111111000000101000000011</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1150,19 +1150,19 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>00101110001110100000000000000101</t>
+          <t>00101110001110100000000000000110</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>00100000111111000000010101010011</t>
+          <t>00100000111111000000101100000011</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1172,19 +1172,19 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>00101110001110100000000000000101</t>
+          <t>00101110001110100000000000000110</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>00100000111111000000100001001110</t>
+          <t>00100000111111000000000000010000</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1194,19 +1194,19 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>00101110001110100000000000000101</t>
+          <t>00101110001110100000000000000111</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>00100000111111000000101111000000</t>
+          <t>00100000111111000000110000011010</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1216,19 +1216,19 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>00101110001110100000000000000101</t>
+          <t>00101110001110100000000000000111</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>00100000111111000000011011011111</t>
+          <t>00100000111111000000010101010011</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1238,19 +1238,19 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>00101110001110100000000000000010</t>
+          <t>00101110001110100000000000000111</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>00100000111111000000010011000000</t>
+          <t>00100000111111000000011100101010</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1267,12 +1267,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>00101110001110100000000000000110</t>
+          <t>00101110001110100000000000000111</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>00100000111111000000011111010011</t>
+          <t>00100000111111000000101111000000</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1282,19 +1282,19 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>00101110001110100000000000000110</t>
+          <t>00101110001110100000000000000111</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>00100000111111000000000101011010</t>
+          <t>00100000111111000000110111100011</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1304,19 +1304,19 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>00101110001110100000000000000110</t>
+          <t>00101110001110100000000000000111</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>00100000111111000000010010111100</t>
+          <t>00100000111111000000011001011100</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1326,19 +1326,19 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>00101110001110100000000000000110</t>
+          <t>00101110001110100000000000000111</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>00100000111111000000011101100000</t>
+          <t>00100000111111000000101111011000</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1348,19 +1348,19 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>00101110001110100000000000000110</t>
+          <t>00101110001110100000000000000111</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>00100000111111000000100000010011</t>
+          <t>00100000111111000000110111011000</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1370,19 +1370,19 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>00101110001110100000000000000110</t>
+          <t>00101110001110100000000000000111</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>00100000111111000000011000010110</t>
+          <t>00100000111111000000100101110101</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
@@ -1404,7 +1404,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>00100000111111000000101000011110</t>
+          <t>00100000111111000000010101000001</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1414,19 +1414,19 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>00101110001110100000000000000111</t>
+          <t>00101110001110100000000000001010</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>00100000111111000000100001011101</t>
+          <t>00100000111111000000100100011100</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1436,19 +1436,19 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>00101110001110100000000000000111</t>
+          <t>00101110001110100000000000001010</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>00100000111111000000100101001001</t>
+          <t>00100000111111000000000001011101</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1458,19 +1458,19 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>00101110001110100000000000000001</t>
+          <t>00101110001110100000000000001010</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>00100000111111000000001110110111</t>
+          <t>00100000111111000000010101010011</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1480,19 +1480,19 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>00101110001110100000000000000111</t>
+          <t>00101110001110100000000000001010</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>00100000111111000000001101111100</t>
+          <t>00100000111111000000101011101010</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1502,19 +1502,19 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>00101110001110100000000000000111</t>
+          <t>00101110001110100000000000001010</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>00100000111111000000101001100101</t>
+          <t>00100000111111000000000100110101</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1524,19 +1524,19 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>00101110001110100000000000000010</t>
+          <t>00101110001110100000000000001010</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>00100000111111000000000001011000</t>
+          <t>00100000111111000000100001001110</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -1553,12 +1553,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>00101110001110100000000000000010</t>
+          <t>00101110001110100000000000001011</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>00100000111111000000000111010101</t>
+          <t>00100000111111000000101000101101</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -1575,12 +1575,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>00101110001110100000000000000111</t>
+          <t>00101110001110100000000000001011</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>00100000111111000000010110001101</t>
+          <t>00100000111111000000010101111110</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -1590,19 +1590,19 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>00101110001110100000000000000010</t>
+          <t>00101110001110100000000000001011</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>00100000111111000000011001110111</t>
+          <t>00100000111111000000101010000100</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -1612,19 +1612,19 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>00101110001110100000000000000010</t>
+          <t>00101110001110100000000000001011</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>00100000111111000000010101110101</t>
+          <t>00100000111111000000010100110100</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -1641,12 +1641,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>00101110001110100000000000001010</t>
+          <t>00101110001110100000000000001011</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>00100000111111000000001010101001</t>
+          <t>00100000111111000000001011101000</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -1656,19 +1656,19 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>00101110001110100000000000000101</t>
+          <t>00101110001110100000000000001011</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>00100000111111000000001010101000</t>
+          <t>00100000111111000000001111111101</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -1685,12 +1685,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>00101110001110100000000000001010</t>
+          <t>00101110001110100000000000001011</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>00100000111111000000001001111001</t>
+          <t>00100000111111000000101001100010</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -1700,19 +1700,19 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>00101110001110100000000000001011</t>
+          <t>00101110001110100000000000001100</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>00100000111111000000010111000001</t>
+          <t>00100000111111000000000001001110</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -1722,19 +1722,19 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>00101110001110100000000000001011</t>
+          <t>00101110001110100000000000001100</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>00100000111111000000011101100111</t>
+          <t>00100000111111000000000010111000</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -1744,19 +1744,19 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>00101110001110100000000000001011</t>
+          <t>00101110001110100000000000001100</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>00100000111111000000100000100110</t>
+          <t>00100000111111000000010001010101</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -1766,19 +1766,19 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>00101110001110100000000000001011</t>
+          <t>00101110001110100000000000001111</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>00100000111111000000100111111110</t>
+          <t>00100000111111000000010111001101</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -1788,19 +1788,19 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>00101110001110100000000000000010</t>
+          <t>00101110001110100000000000001111</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>00100000111111000000011001000100</t>
+          <t>00100000111111000000101010000100</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -1810,19 +1810,19 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>00101110001110100000000000001100</t>
+          <t>00101110001110100000000000001111</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>00100000111111000000000100000001</t>
+          <t>00100000111111000000000000000111</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -1832,19 +1832,19 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>00101110001110100000000000001100</t>
+          <t>00101110001110100000000000001111</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>00100000111111000000011100011001</t>
+          <t>00100000111111000000010100000101</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -1854,19 +1854,19 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>00101110001110100000000000000010</t>
+          <t>00101110001110100000000000001111</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>00100000111111000000000000101100</t>
+          <t>00100000111111000000000101101100</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -1876,19 +1876,19 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>00101110001110100000000000000010</t>
+          <t>00101110001110100000000000010001</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>00100000111111000000001110000011</t>
+          <t>00100000111111000000101011110100</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -1898,19 +1898,19 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>00101110001110100000000000001111</t>
+          <t>00101110001110100000000000010001</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>00100000111111000000000001111111</t>
+          <t>00100000111111000000011100111011</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -1920,19 +1920,19 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>00101110001110100000000000000010</t>
+          <t>00101110001110100000000000010001</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>00100000111111000000101100111000</t>
+          <t>00100000111111000000000000010000</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -1942,19 +1942,19 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>00101110001110100000000000001111</t>
+          <t>00101110001110100000000000010001</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>00100000111111000000101000010111</t>
+          <t>00100000111111000000110111100011</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -1964,19 +1964,19 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>00101110001110100000000000000010</t>
+          <t>00101110001110100000000000010001</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>00100000111111000000010010011010</t>
+          <t>00100000111111000000001111101111</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -1986,19 +1986,19 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>00101110001110100000000000001111</t>
+          <t>00101110001110100000000000010011</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>00100000111111000000000101101100</t>
+          <t>00100000111111000000011100010101</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -2008,19 +2008,19 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>00101110001110100000000000001111</t>
+          <t>00101110001110100000000000010011</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>00100000111111000000100010000010</t>
+          <t>00100000111111000000000010110111</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -2030,19 +2030,19 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>00101110001110100000000000010001</t>
+          <t>00101110001110100000000000010011</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>00100000111111000000101100110010</t>
+          <t>00100000111111000000001010010000</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -2052,19 +2052,19 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>00101110001110100000000000010001</t>
+          <t>00101110001110100000000000010011</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>00100000111111000000011111100110</t>
+          <t>00100000111111000000010011111111</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -2074,19 +2074,19 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>00101110001110100000000000010001</t>
+          <t>00101110001110100000000000010011</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>00100000111111000000010101000001</t>
+          <t>00100000111111000000101001100010</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -2096,19 +2096,19 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>00101110001110100000000000000011</t>
+          <t>00101110001110100000000000010101</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>00100000111111000000011010110101</t>
+          <t>00100000111111000000011001000011</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -2118,19 +2118,19 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>00101110001110100000000000000000</t>
+          <t>00101110001110100000000000010101</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>00100000111111000000001111101111</t>
+          <t>00100000111111000000010110001010</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -2140,19 +2140,19 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>00101110001110100000000000010011</t>
+          <t>00101110001110100000000000010101</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>00100000111111000000100101111010</t>
+          <t>00100000111111000000101000001110</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -2162,19 +2162,19 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>00101110001110100000000000010011</t>
+          <t>00101110001110100000000000010101</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>00100000111111000000011011100000</t>
+          <t>00100000111111000000011011011111</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -2184,19 +2184,19 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>00101110001110100000000000010011</t>
+          <t>00101110001110100000000000010101</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>00100000111111000000011101011001</t>
+          <t>00100000111111000000001110001100</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -2206,19 +2206,19 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>00101110001110100000000000010101</t>
+          <t>00101110001110100000000000010110</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>00100000111111000000010100000101</t>
+          <t>00100000111111000000000010111000</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -2228,19 +2228,19 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>00101110001110100000000000000011</t>
+          <t>00101110001110100000000000010110</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>00100000111111000000100001001100</t>
+          <t>00100000111111000000101000101101</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -2250,19 +2250,19 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>00101110001110100000000000010101</t>
+          <t>00101110001110100000000000010110</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>00100000111111000000000101110100</t>
+          <t>00100000111111000000000000000111</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -2272,19 +2272,19 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>00101110001110100000000000000011</t>
+          <t>00101110001110100000000000010110</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>00100000111111000000011011110111</t>
+          <t>00100000111111000000000001010001</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -2294,7 +2294,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
@@ -2306,7 +2306,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>00100000111111000000001100110101</t>
+          <t>00100000111111000000100101111010</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
@@ -2328,7 +2328,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>00100000111111000000011000001100</t>
+          <t>00100000111111000000010101111101</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -2338,19 +2338,19 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>00101110001110100000000000000101</t>
+          <t>00101110001110100000000000010110</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>00100000111111000000101001011101</t>
+          <t>00100000111111000000001100110101</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -2360,19 +2360,19 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>00101110001110100000000000000101</t>
+          <t>00101110001110100000000000010110</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>00100000111111000000000111000001</t>
+          <t>00100000111111000000010001010011</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -2389,12 +2389,12 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>00101110001110100000000000000101</t>
+          <t>00101110001110100000000000010110</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>00100000111111000000010000111000</t>
+          <t>00100000111111000000010100000101</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
@@ -2416,7 +2416,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>00100000111111000000000011011001</t>
+          <t>00100000111111000000010101010011</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -2426,19 +2426,19 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>00101110001110100000000000000101</t>
+          <t>00101110001110100000000000010111</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>00100000111111000000000001101001</t>
+          <t>00100000111111000000101100110101</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -2448,19 +2448,19 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>00101110001110100000000000010110</t>
+          <t>00101110001110100000000000010111</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>00100000111111000000010010100000</t>
+          <t>00100000111111000000010101100000</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -2470,19 +2470,19 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>00101110001110100000000000010110</t>
+          <t>00101110001110100000000000010111</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>00100000111111000000001110001100</t>
+          <t>00100000111111000000001110101011</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -2492,19 +2492,19 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>00101110001110100000000000010110</t>
+          <t>00101110001110100000000000010111</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>00100000111111000000000000010010</t>
+          <t>00100000111111000000101010001110</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -2514,19 +2514,19 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>00101110001110100000000000000101</t>
+          <t>00101110001110100000000000010111</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>00100000111111000000101010001110</t>
+          <t>00100000111111000000011111110001</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -2536,19 +2536,19 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>00101110001110100000000000000101</t>
+          <t>00101110001110100000000000011001</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>00100000111111000000100001111110</t>
+          <t>00100000111111000000000010010001</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -2558,19 +2558,19 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>00101110001110100000000000010111</t>
+          <t>00101110001110100000000000011001</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>00100000111111000000010110110100</t>
+          <t>00100000111111000000011010001100</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -2580,19 +2580,19 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>00101110001110100000000000010111</t>
+          <t>00101110001110100000000000011001</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>00100000111111000000100101001100</t>
+          <t>00100000111111000000100111000100</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -2602,19 +2602,19 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>00101110001110100000000000000101</t>
+          <t>00101110001110100000000000011001</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>00100000111111000000010110110000</t>
+          <t>00100000111111000000011111010011</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -2624,7 +2624,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>00100000111111000000000000010000</t>
+          <t>00100000111111000000001110001100</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
@@ -2658,7 +2658,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>00100000111111000000000111101100</t>
+          <t>00100000111111000000000000010000</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -2668,7 +2668,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
@@ -2680,7 +2680,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>00100000111111000000101100001101</t>
+          <t>00100000111111000000100111110110</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -2690,7 +2690,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
@@ -2702,7 +2702,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>00100000111111000000100101110110</t>
+          <t>00100000111111000000011000001100</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -2712,7 +2712,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
@@ -2724,7 +2724,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>00100000111111000000000010110111</t>
+          <t>00100000111111000000100010100001</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -2734,7 +2734,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
@@ -2746,7 +2746,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>00100000111111000000011000110101</t>
+          <t>00100000111111000000010011110100</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -2756,7 +2756,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
@@ -2768,7 +2768,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>00100000111111000000011001000011</t>
+          <t>00100000111111000000001010010010</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -2778,19 +2778,19 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>00101110001110100000000000000101</t>
+          <t>00101110001110100000000000011010</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>00100000111111000000001110101100</t>
+          <t>00100000111111000000100111100110</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -2800,19 +2800,19 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>00101110001110100000000000000101</t>
+          <t>00101110001110100000000000011010</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>00100000111111000000011111101110</t>
+          <t>00100000111111000000101011010110</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -2822,19 +2822,19 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>00101110001110100000000000011010</t>
+          <t>00101110001110100000000000011011</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>00100000111111000000010111001101</t>
+          <t>00100000111111000000101000000011</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -2844,19 +2844,19 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>00101110001110100000000000000101</t>
+          <t>00101110001110100000000000011011</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>00100000111111000000011110001000</t>
+          <t>00100000111111000000010000111000</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -2873,12 +2873,12 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>00101110001110100000000000011011</t>
+          <t>00101110001110100000000000011100</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>00100000111111000000100111101010</t>
+          <t>00100000111111000000001001010000</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -2888,19 +2888,19 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>00101110001110100000000000011011</t>
+          <t>00101110001110100000000000011100</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>00100000111111000000101001111000</t>
+          <t>00100000111111000000001011001101</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -2910,19 +2910,19 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>00101110001110100000000000011011</t>
+          <t>00101110001110100000000000011100</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>00100000111111000000100110101001</t>
+          <t>00100000111111000000010100010110</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -2932,7 +2932,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
@@ -2944,7 +2944,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>00100000111111000000101011000110</t>
+          <t>00100000111111000000011011101110</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
@@ -2966,7 +2966,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>00100000111111000000100010110101</t>
+          <t>00100000111111000000010001001100</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -2976,19 +2976,19 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>00101110001110100000000000011100</t>
+          <t>00101110001110100000000000011101</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>00100000111111000000100010000101</t>
+          <t>00100000111111000000101000101110</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -2998,19 +2998,19 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>00101110001110100000000000011100</t>
+          <t>00101110001110100000000000011101</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>00100000111111000000010100010110</t>
+          <t>00100000111111000000000110100100</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -3020,19 +3020,19 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>00101110001110100000000000011100</t>
+          <t>00101110001110100000000000011101</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>00100000111111000000010001001100</t>
+          <t>00100000111111000000011101000110</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -3042,7 +3042,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>00100000111111000000000110000111</t>
+          <t>00100000111111000000000110110000</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -3064,19 +3064,19 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>00101110001110100000000000000101</t>
+          <t>00101110001110100000000000011101</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>00100000111111000000100001010110</t>
+          <t>00100000111111000000000111101100</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -3098,7 +3098,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>00100000111111000000010111010100</t>
+          <t>00100000111111000000010101010011</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -3108,19 +3108,19 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>00101110001110100000000000011101</t>
+          <t>00101110001110100000000000011110</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>00100000111111000000000101011000</t>
+          <t>00100000111111000000010011101100</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -3130,19 +3130,19 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>00101110001110100000000000011101</t>
+          <t>00101110001110100000000000011110</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>00100000111111000000101100110011</t>
+          <t>00100000111111000000010101010110</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -3152,19 +3152,19 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>00101110001110100000000000011101</t>
+          <t>00101110001110100000000000011110</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>00100000111111000000001010011111</t>
+          <t>00100000111111000000011000010110</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -3174,19 +3174,19 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>00101110001110100000000000011101</t>
+          <t>00101110001110100000000000011110</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>00100000111111000000010111100110</t>
+          <t>00100000111111000000101001111000</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -3196,19 +3196,19 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>00101110001110100000000000011101</t>
+          <t>00101110001110100000000000011110</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>00100000111111000000010100110100</t>
+          <t>00100000111111000000001011001101</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -3218,19 +3218,19 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>00101110001110100000000000011101</t>
+          <t>00101110001110100000000000100000</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>00100000111111000000100100001001</t>
+          <t>00100000111111000000001110001100</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -3240,19 +3240,19 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>00101110001110100000000000000110</t>
+          <t>00101110001110100000000000100000</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>00100000111111000000010010110001</t>
+          <t>00100000111111000000100010110101</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -3262,19 +3262,19 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>00101110001110100000000000011110</t>
+          <t>00101110001110100000000000100000</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>00100000111111000000001010101010</t>
+          <t>00100000111111000000011000001100</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -3284,19 +3284,19 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>00101110001110100000000000011110</t>
+          <t>00101110001110100000000000100000</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>00100000111111000000011011110011</t>
+          <t>00100000111111000000010101110101</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -3306,19 +3306,19 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>00101110001110100000000000000110</t>
+          <t>00101110001110100000000000100000</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>00100000111111000000011100010101</t>
+          <t>00100000111111000000101001010111</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -3328,19 +3328,19 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>00101110001110100000000000000110</t>
+          <t>00101110001110100000000000100000</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>00100000111111000000000001001110</t>
+          <t>00100000111111000000100110111100</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -3350,19 +3350,19 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>00101110001110100000000000000110</t>
+          <t>00101110001110100000000000100000</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>00100000111111000000100110000110</t>
+          <t>00100000111111000000100010000010</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -3372,19 +3372,19 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>00101110001110100000000000011110</t>
+          <t>00101110001110100000000000100001</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>00100000111111000000100101101111</t>
+          <t>00100000111111000000011010111110</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -3394,19 +3394,19 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>00101110001110100000000000000110</t>
+          <t>00101110001110100000000000100001</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>00100000111111000000010101100000</t>
+          <t>00100000111111000000101100001101</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -3416,19 +3416,19 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>00101110001110100000000000000110</t>
+          <t>00101110001110100000000000100001</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>00100000111111000000101001011010</t>
+          <t>00100000111111000000011010110010</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -3438,19 +3438,19 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>00101110001110100000000000100000</t>
+          <t>00101110001110100000000000100001</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>00100000111111000000100111011111</t>
+          <t>00100000111111000000010011111111</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -3460,19 +3460,19 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>00101110001110100000000000100000</t>
+          <t>00101110001110100000000000100001</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>00100000111111000000000011010010</t>
+          <t>00100000111111000000000000010000</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -3482,19 +3482,19 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>00101110001110100000000000100000</t>
+          <t>00101110001110100000000000100001</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>00100000111111000000010110001010</t>
+          <t>00100000111111000000101000010101</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -3504,19 +3504,19 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>00101110001110100000000000100000</t>
+          <t>00101110001110100000000000100011</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>00100000111111000000011101111011</t>
+          <t>00100000111111000000001110001100</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -3526,19 +3526,19 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>00101110001110100000000000100000</t>
+          <t>00101110001110100000000000100011</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>00100000111111000000011010110010</t>
+          <t>00100000111111000000100111001111</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -3548,19 +3548,19 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>00101110001110100000000000100000</t>
+          <t>00101110001110100000000000100011</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>00100000111111000000011000111110</t>
+          <t>00100000111111000000100011001001</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -3570,19 +3570,19 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>00101110001110100000000000100000</t>
+          <t>00101110001110100000000000100011</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>00100000111111000000000000000111</t>
+          <t>00100000111111000000100111011111</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -3592,19 +3592,19 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>00101110001110100000000000100000</t>
+          <t>00101110001110100000000000100100</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>00100000111111000000011100001010</t>
+          <t>00100000111111000000000001111111</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -3614,19 +3614,19 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>00101110001110100000000000100001</t>
+          <t>00101110001110100000000000100100</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>00100000111111000000100100000010</t>
+          <t>00100000111111000000101101001111</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -3636,19 +3636,19 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>00101110001110100000000000100001</t>
+          <t>00101110001110100000000000100100</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>00100000111111000000010111001110</t>
+          <t>00100000111111000000000010001111</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -3658,19 +3658,19 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>00101110001110100000000000100001</t>
+          <t>00101110001110100000000000100100</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>00100000111111000000001101011111</t>
+          <t>00100000111111000000011000001100</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -3680,19 +3680,19 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>00101110001110100000000000100001</t>
+          <t>00101110001110100000000000100100</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>00100000111111000000001011001101</t>
+          <t>00100000111111000000100000000011</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -3702,19 +3702,19 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>00101110001110100000000000100001</t>
+          <t>00101110001110100000000000100010</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>00100000111111000000001011000011</t>
+          <t>00100000111111000000111001001001</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -3724,19 +3724,19 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>00101110001110100000000000100001</t>
+          <t>00101110001110100000000000100010</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>00100000111111000000001011111101</t>
+          <t>00100000111111000000101101101111</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -3746,19 +3746,19 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>00101110001110100000000000100001</t>
+          <t>00101110001110100000000000100010</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>00100000111111000000101110101111</t>
+          <t>00100000111111000000000110110110</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -3768,19 +3768,19 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>00101110001110100000000000100001</t>
+          <t>00101110001110100000000000100010</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>00100000111111000000101101110001</t>
+          <t>00100000111111000000011100101110</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -3790,200 +3790,200 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>00101110001110100000000000100001</t>
+          <t>00000000000000000000000011001101</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>00100000111111000000000011010011</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>00100001011110100000000010011000</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>00101110001110100000000000000111</t>
+          <t>00000000000000000000000011000101</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>00100000111111000000000100101101</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>00100001011110100000000010011001</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>00101110001110100000000000100011</t>
+          <t>00000000000000000000000011011110</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>00100000111111000000010110000101</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>00100001011110100000000010011010</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>00101110001110100000000000100100</t>
+          <t>00000000000000000000000010011010</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>00100000111111000000000010100100</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>00100001011110100000000010011011</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>00101110001110100000000000100100</t>
+          <t>00000000000000000000000010011011</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>00100000111111000000011111100001</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>00100001011110100000000010011100</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>00101110001110100000000000100100</t>
+          <t>00000000000000000000000000001111</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>00100000111111000000011100111011</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>00100001011110100000000010011101</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>00101110001110100000000000100100</t>
+          <t>00000000000000000000000010111010</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>00100000111111000000011001011100</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>00100001011110100000000010011110</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>00101110001110100000000000100100</t>
+          <t>00000000000000000000000011000001</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>00100000111111000000010101111101</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>00100001011110100000000010011111</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>00101110001110100000000000000101</t>
+          <t>00000000000000000000000001011010</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>00100000111111000000000110110110</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>00100001011110100000000010100000</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -3995,105 +3995,105 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>00101110001110100000000000100010</t>
+          <t>00000000000000000000000010111111</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>00100000111111000000100110011011</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>00100001011110100000000010100001</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>00101110001110100000000000000111</t>
+          <t>00000000000000000000000010100001</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>00100000111111000000001111111101</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>00100001011110100000000010100010</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>00101110001110100000000000000111</t>
+          <t>00000000000000000000000011000111</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>00100000111111000000000100010101</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>00100001011110100000000010100011</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>00101110001110100000000000000111</t>
+          <t>00000000000000000000000011100011</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>00100000111111000000000111111001</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>00100001011110100000000010100100</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>00101110001110100000000000000111</t>
+          <t>00000000000000000000000010100111</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>00100000111111000000100101110101</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>00100001011110100000000010100101</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -4105,215 +4105,215 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>00101110001110100000000000000111</t>
+          <t>00000000000000000000000011001011</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>00100000111111000000011111011001</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>00100001011110100000000010100110</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>00101110001110100000000000000111</t>
+          <t>00000000000000000000000000111001</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>00100000111111000000100000111001</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>00100001011110100000000010100111</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>00101110001110100000000000000111</t>
+          <t>00000000000000000000000011010101</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>00100000111111000000100000010101</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>00100001011110100000000010101000</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>00101110001110100000000000000111</t>
+          <t>00000000000000000000000010110101</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>00100000111111000000001100110011</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>00100001011110100000000010101001</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>00101110001110100000000000001010</t>
+          <t>00000000000000000000000011000100</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>00100000111111000000100000010111</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>00100001011110100000000010101010</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>00101110001110100000000000001010</t>
+          <t>00000000000000000000000011100000</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>00100000111111000000100111110001</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>00100001011110100000000010101011</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>00101110001110100000000000001010</t>
+          <t>00000000000000000000000010101011</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>00100000111111000000101110111101</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>00100001011110100000000010101100</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>00101110001110100000000000001010</t>
+          <t>00000000000000000000000010101100</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>00100000111111000000001110001110</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>00100001011110100000000010101101</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>00101110001110100000000000001010</t>
+          <t>00000000000000000000000100001001</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>00100000111111000000000111111011</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>00100001011110100000000010101110</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>00101110001110100000000000000111</t>
+          <t>00000000000000000000000010111000</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>00100000111111000000000101100011</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>00100001011110100000000010101111</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -4325,17 +4325,17 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>00101110001110100000000000000111</t>
+          <t>00000000000000000000000000000101</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>00100000111111000000100110111100</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>00100001011110100000000010110000</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -4347,17 +4347,17 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>00101110001110100000000000000111</t>
+          <t>00000000000000000000000010011001</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>00100000111111000000000111111010</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>00100001011110100000000010110001</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -4369,215 +4369,215 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>00101110001110100000000000001010</t>
+          <t>00000000000000000000000010110001</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>00100000111111000000001010100111</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>00100001011110100000000010110010</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>00101110001110100000000000001011</t>
+          <t>00000000000000000000000010110010</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>00100000111111000000100100100101</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>00100001011110100000000010110011</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>00101110001110100000000000001011</t>
+          <t>00000000000000000000000010110011</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>00100000111111000000000000110000</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>00100001011110100000000010110100</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>00101110001110100000000000001011</t>
+          <t>00000000000000000000000010100000</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>00100000111111000000001010010011</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>00100001011110100000000010110101</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>00101110001110100000000000001011</t>
+          <t>00000000000000000000000011110000</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>00100000111111000000011111111101</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>00100001011110100000000010110110</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>00101110001110100000000000001100</t>
+          <t>00000000000000000000000010110110</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>00100000111111000000100001011110</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>00100001011110100000000010110111</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>00101110001110100000000000001100</t>
+          <t>00000000000000000000000010100011</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>00100000111111000000011111101000</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>00100001011110100000000010111000</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>00101110001110100000000000001100</t>
+          <t>00000000000000000000000011100100</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>00100000111111000000101101100100</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>00100001011110100000000010111001</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>00101110001110100000000000001100</t>
+          <t>00000000000000000000000010111001</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>00100000111111000000011101001101</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>00100001011110100000000010111010</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>00101110001110100000000000000111</t>
+          <t>00000000000000000000000010011101</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>00100000111111000000101110101011</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>00100001011110100000000010111011</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -4589,83 +4589,83 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>00101110001110100000000000001100</t>
+          <t>00000000000000000000000010011110</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>00100000111111000000000110110000</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>00100001011110100000000010111100</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>00101110001110100000000000001111</t>
+          <t>00000000000000000000000010110000</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>00100000111111000000100011100010</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>00100001011110100000000010111101</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>00101110001110100000000000001111</t>
+          <t>00000000000000000000000011010111</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>00100000111111000000001000010000</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>00100001011110100000000010111110</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>00101110001110100000000000000111</t>
+          <t>00000000000000000000000010011111</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>00100000111111000000011111000110</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>00100001011110100000000010111111</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -4677,83 +4677,83 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>00101110001110100000000000001111</t>
+          <t>00000000000000000000000001101101</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>00100000111111000000000101000000</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>00100001011110100000000011000000</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>00101110001110100000000000001111</t>
+          <t>00000000000000000000000011010100</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>00100000111111000000011100101010</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>00100001011110100000000011000001</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>00101110001110100000000000001111</t>
+          <t>00000000000000000000000011100111</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>00100000111111000000010011100111</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>00100001011110100000000011000010</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>00101110001110100000000000001010</t>
+          <t>00000000000000000000000000111000</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>00100000111111000000011111011111</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>00100001011110100000000011000011</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -4765,83 +4765,83 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>00101110001110100000000000001111</t>
+          <t>00000000000000000000000000010001</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>00100000111111000000101101110100</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>00100001011110100000000011000100</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>00101110001110100000000000001111</t>
+          <t>00000000000000000000000010101110</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>00100000111111000000000111110001</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>00100001011110100000000011000101</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>00101110001110100000000000010001</t>
+          <t>00000000000000000000000010100100</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>00100000111111000000100011011110</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>00100001011110100000000011000110</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>00101110001110100000000000001010</t>
+          <t>00000000000000000000000010100110</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>00100000111111000000001110010110</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>00100001011110100000000011000111</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -4853,17 +4853,17 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>00101110001110100000000000001010</t>
+          <t>00000000000000000000000000100001</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>00100000111111000000001101100000</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>00100001011110100000000011001000</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -4875,237 +4875,237 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>00101110001110100000000000010101</t>
+          <t>00000000000000000000000001100001</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>00100000111111000000011010010110</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>00100001011110100000000011001001</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>00101110001110100000000000010101</t>
+          <t>00000000000000000000000011001110</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>00100000111111000000000000001110</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>00100001011110100000000011001010</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>00101110001110100000000000010101</t>
+          <t>00000000000000000000000010100101</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>00100000111111000000100011110101</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>00100001011110100000000011001011</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>00101110001110100000000000010101</t>
+          <t>00000000000000000000000010101001</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>00100000111111000000101000101101</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>00100001011110100000000011001100</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>00101110001110100000000000010101</t>
+          <t>00000000000000000000000010010110</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>00100000111111000000000010011101</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>00100001011110100000000011001101</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>00101110001110100000000000010101</t>
+          <t>00000000000000000000000010001111</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>00100000111111000000000111111101</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>00100001011110100000000011001110</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>00101110001110100000000000010101</t>
+          <t>00000000000000000000000010000100</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>00100000111111000000001101001010</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>00100001011110100000000011001111</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>00101110001110100000000000010101</t>
+          <t>00000000000000000000000011100010</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>00100000111111000000001100011010</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>00100001011110100000000011010000</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>00101110001110100000000000010101</t>
+          <t>00000000000000000000000001000001</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>00100000111111000000001001111110</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>00100001011110100000000011010001</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>00101110001110100000000000010101</t>
+          <t>00000000000000000000000001011110</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>00100000111111000000000000001001</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>00100001011110100000000011010010</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>00101110001110100000000000001010</t>
+          <t>00000000000000000000000010111100</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>00100000111111000000000000011110</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>00100001011110100000000011010011</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -5117,17 +5117,17 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>00101110001110100000000000001111</t>
+          <t>00000000000000000000000010011100</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>00100000111111000000001110110110</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>00100001011110100000000011010100</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -5139,61 +5139,61 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>00101110001110100000000000010110</t>
+          <t>00000000000000000000000010010101</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>00100000111111000000101011100110</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>00100001011110100000000011010101</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>00101110001110100000000000010110</t>
+          <t>00000000000000000000000001100100</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>00100000111111000000010010011001</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>00100001011110100000000011010110</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>00101110001110100000000000001111</t>
+          <t>00000000000000000000000000101111</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>00100000111111000000100110011010</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>00100001011110100000000011010111</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -5205,39 +5205,39 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>00101110001110100000000000010110</t>
+          <t>00000000000000000000000011011011</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>00100000111111000000001010010010</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>00100001011110100000000011011000</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>00101110001110100000000000001111</t>
+          <t>00000000000000000000000001000110</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>00100000111111000000011100101011</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>00100001011110100000000011011001</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -5249,61 +5249,61 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>00101110001110100000000000010110</t>
+          <t>00000000000000000000000000011101</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>00100000111111000000101000101001</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>00100001011110100000000011011010</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>00101110001110100000000000010110</t>
+          <t>00000000000000000000000011101110</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>00100000111111000000010010001001</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>00100001011110100000000011011011</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>00101110001110100000000000001111</t>
+          <t>00000000000000000000000010111101</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>00100000111111000000011001101101</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>00100001011110100000000011011100</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -5315,17 +5315,17 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>00101110001110100000000000001111</t>
+          <t>00000000000000000000000011100101</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>00100000111111000000011010001100</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>00100001011110100000000011011101</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -5337,83 +5337,83 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>00101110001110100000000000010111</t>
+          <t>00000000000000000000000010011000</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>00100000111111000000101011111100</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>00100001011110100000000011011110</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>00101110001110100000000000010111</t>
+          <t>00000000000000000000000000000001</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>00100000111111000000011010011110</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>00100001011110100000000011011111</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>00101110001110100000000000010111</t>
+          <t>00000000000000000000000011000010</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>00100000111111000000100111011001</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>00100001011110100000000011100000</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>00101110001110100000000000010001</t>
+          <t>00000000000000000000000011000110</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>00100000111111000000100101110101</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>00100001011110100000000011100001</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -5425,281 +5425,281 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>00101110001110100000000000011001</t>
+          <t>00000000000000000000000011001000</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>00100000111111000000011100101110</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>00100001011110100000000011100010</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>00101110001110100000000000011001</t>
+          <t>00000000000000000000000010100010</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>00100000111111000000110110001101</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>00100001011110100000000011100011</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>00101110001110100000000000011001</t>
+          <t>00000000000000000000000010110111</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>00100000111111000000100111110110</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>00100001011110100000000011100100</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>00101110001110100000000000011001</t>
+          <t>00000000000000000000000011001100</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>00100000111111000000010101110011</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>00100001011110100000000011100101</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>00101110001110100000000000011001</t>
+          <t>00000000000000000000000000000010</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>00100000111111000000000010010001</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>00100001011110100000000011100110</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>00101110001110100000000000011001</t>
+          <t>00000000000000000000000000100111</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>00100000111111000000000101010100</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>00100001011110100000000011100111</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>00101110001110100000000000011001</t>
+          <t>00000000000000000000000011001010</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>00100000111111000000101111110111</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>00100001011110100000000011101000</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>00101110001110100000000000011001</t>
+          <t>00000000000000000000000011011111</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>00100000111111000000111001010110</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>00100001011110100000000011101001</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>00101110001110100000000000011001</t>
+          <t>00000000000000000000000000001101</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>00100000111111000000100000001011</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>00100001011110100000000011101010</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>00101110001110100000000000011001</t>
+          <t>00000000000000000000000011110001</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>00100000111111000000101010000001</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>00100001011110100000000011101011</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>00101110001110100000000000011010</t>
+          <t>00000000000000000000000000011001</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>00100000111111000000011010111111</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>00100001011110100000000011101100</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>00101110001110100000000000011010</t>
+          <t>00000000000000000000000001100000</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>00100000111111000000000010010000</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>00100001011110100000000011101101</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>00101110001110100000000000010001</t>
+          <t>00000000000000000000000011011101</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>00100000111111000000100110011010</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>00100001011110100000000011101110</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -5711,83 +5711,83 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>00101110001110100000000000011010</t>
+          <t>00000000000000000000000001000100</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>00100000111111000000000000110111</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>00100001011110100000000011101111</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>00101110001110100000000000011011</t>
+          <t>00000000000000000000000010110100</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>00100000111111000000010110110111</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>00100001011110100000000011110000</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>00101110001110100000000000011011</t>
+          <t>00000000000000000000000011101001</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>00100000111111000000100100000110</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>00100001011110100000000011110001</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>00101110001110100000000000010001</t>
+          <t>00000000000000000000000010001010</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>00100000111111000000000000011110</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>00100001011110100000000011110010</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
@@ -5799,215 +5799,215 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>00101110001110100000000000011011</t>
+          <t>00000000000000000000000011010000</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>00100000111111000000101000010010</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>00100001011110100000000011110011</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>00101110001110100000000000011100</t>
+          <t>00000000000000000000000001011001</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>00100000111111000000001001010000</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>00100001011110100000000011110100</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>00101110001110100000000000011100</t>
+          <t>00000000000000000000000010010000</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>00100000111111000000011000001000</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>00100001011110100000000011110101</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>00101110001110100000000000011101</t>
+          <t>00000000000000000000000001011000</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>00100000111111000000000010111000</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>00100001011110100000000011110110</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>00101110001110100000000000011101</t>
+          <t>00000000000000000000000001000101</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>00100000111111000000111000111111</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>00100001011110100000000011110111</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>00101110001110100000000000011101</t>
+          <t>00000000000000000000000011110111</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>00100000111111000000100101010011</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>00100001011110100000000011111000</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>00101110001110100000000000011101</t>
+          <t>00000000000000000000000011111000</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>00100000111111000000110000010100</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>00100001011110100000000011111001</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>00101110001110100000000000011101</t>
+          <t>00000000000000000000000011111001</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>00100000111111000000100010001010</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>00100001011110100000000011111010</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>00101110001110100000000000011101</t>
+          <t>00000000000000000000000011111010</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>00100000111111000000000010111101</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>00100001011110100000000011111011</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>00101110001110100000000000010101</t>
+          <t>00000000000000000000000011111011</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>00100000111111000000001110110000</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>00100001011110100000000011111100</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
@@ -6019,61 +6019,61 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>00101110001110100000000000011110</t>
+          <t>00000000000000000000000011111100</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>00100000111111000000000001001111</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>00100001011110100000000011111101</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>00101110001110100000000000011110</t>
+          <t>00000000000000000000000011111101</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>00100000111111000000101100000011</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>00100001011110100000000011111110</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>00101110001110100000000000010110</t>
+          <t>00000000000000000000000011111110</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>00100000111111000000101111011000</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>00100001011110100000000011111111</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
@@ -6085,39 +6085,39 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>00101110001110100000000000011110</t>
+          <t>00000000000000000000000011111111</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>00100000111111000000000001010110</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>00100001011110100000000100000000</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>00101110001110100000000000010110</t>
+          <t>00000000000000000000000100000000</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>00100000111111000000011000101111</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>00100001011110100000000100000001</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
@@ -6129,523 +6129,523 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>00101110001110100000000000011110</t>
+          <t>00000000000000000000000100000001</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>00100000111111000000101000000011</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>00100001011110100000000100000010</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>00101110001110100000000000011110</t>
+          <t>00000000000000000000000100000010</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>00100000111111000000101110111000</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>00100001011110100000000100000011</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>00101110001110100000000000011110</t>
+          <t>00000000000000000000000100000011</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>00100000111111000000000101100100</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>00100001011110100000000100000100</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>00101110001110100000000000011110</t>
+          <t>00000000000000000000000100000100</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>00100000111111000000000001110111</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>00100001011110100000000100000101</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>00101110001110100000000000011111</t>
+          <t>00000000000000000000000100000101</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>00100000111111000000000101001000</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>00100001011110100000000100000110</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>00101110001110100000000000011111</t>
+          <t>00000000000000000000000100000110</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>00100000111111000000010011101100</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>00100001011110100000000100000111</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>00101110001110100000000000100000</t>
+          <t>00000000000000000000000100000111</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>00100000111111000000101101001111</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>00100001011110100000000100001000</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>00101110001110100000000000100000</t>
+          <t>00000000000000000000000010101101</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>00100000111111000000101101111100</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>00100001011110100000000100001001</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>00101110001110100000000000100000</t>
+          <t>00000000000000000000000100001011</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>00100000111111000000011100110101</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>00100001011110100000000100001010</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>00101110001110100000000000100000</t>
+          <t>00000000000000000000000100001100</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>00100000111111000000001010010000</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>00100001011110100000000100001011</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>00101110001110100000000000100000</t>
+          <t>00000000000000000000000100001101</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>00100000111111000000000010011111</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>00100001011110100000000100001100</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>00101110001110100000000000100000</t>
+          <t>00000000000000000000000100001110</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>00100000111111000000010111011011</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>00100001011110100000000100001101</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>00101110001110100000000000100000</t>
+          <t>00000000000000000000000100001111</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>00100000111111000000101000010101</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>00100001011110100000000100001110</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>00101110001110100000000000100000</t>
+          <t>00000000000000000000000100010000</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>00100000111111000000001111010101</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>00100001011110100000000100001111</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>00101110001110100000000000100001</t>
+          <t>00000000000000000000000100010001</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>00100000111111000000001110000110</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>00100001011110100000000100010000</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>00101110001110100000000000100001</t>
+          <t>00000000000000000000000100010010</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>00100000111111000000100101000111</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>00100001011110100000000100010001</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>00101110001110100000000000100001</t>
+          <t>00000000000000000000000100010011</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>00100000111111000000000001011111</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>00100001011110100000000100010010</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>00101110001110100000000000100011</t>
+          <t>00000000000000000000000100010100</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>00100000111111000000101100110101</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>00100001011110100000000100010011</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>00101110001110100000000000100011</t>
+          <t>00000000000000000000000100010101</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>00100000111111000000101100111101</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>00100001011110100000000100010100</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>00101110001110100000000000100011</t>
+          <t>00000000000000000000000100010110</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>00100000111111000000010000000000</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>00100001011110100000000100010101</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>00101110001110100000000000100011</t>
+          <t>00000000000000000000000100010111</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>00100000111111000000001110101011</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>00100001011110100000000100010110</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>00101110001110100000000000100011</t>
+          <t>00000000000000000000000100011000</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>00100000111111000000100000111111</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>00100001011110100000000100010111</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>00101110001110100000000000100100</t>
+          <t>00000000000000000000000100011001</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>00100000111111000000011111011011</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>00100001011110100000000100011000</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>00101110001110100000000000010110</t>
+          <t>00000000000000000000000100011010</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>00100000111111000000010101110101</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>00100001011110100000000100011001</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
@@ -6657,17 +6657,17 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>00101110001110100000000000010110</t>
+          <t>00000000000000000000000100011011</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>00100000111111000000010110011110</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>00100001011110100000000100011010</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
@@ -6679,39 +6679,39 @@
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>00101110001110100000000000100100</t>
+          <t>00000000000000000000000100011100</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>00100000111111000000011001111011</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>00100001011110100000000100011011</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>00101110001110100000000000010110</t>
+          <t>00000000000000000000000100011101</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>00100000111111000000100010100001</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>00100001011110100000000100011100</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
@@ -6723,259 +6723,259 @@
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>00101110001110100000000000100100</t>
+          <t>00000000000000000000000100011110</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>00100000111111000000101011011111</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>00100001011110100000000100011101</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>00101110001110100000000000100100</t>
+          <t>00000000000000000000000100011111</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>00100000111111000000110000111011</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>00100001011110100000000100011110</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>00101110001110100000000000100100</t>
+          <t>00000000000000000000000100100000</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>00100000111111000000100100011010</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>00100001011110100000000100011111</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>00101110001110100000000000100100</t>
+          <t>00000000000000000000000100100001</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>00100000111111000000110000011010</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>00100001011110100000000100100000</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>00101110001110100000000000100100</t>
+          <t>00000000000000000000000100100010</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>00100000111111000000000110000110</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>00100001011110100000000100100001</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>00101110001110100000000000100010</t>
+          <t>00000000000000000000000100100011</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>00100000111111000000001010110011</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>00100001011110100000000100100010</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>00101110001110100000000000100010</t>
+          <t>00000000000000000000000100100100</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>00100000111111000000100110001010</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>00100001011110100000000100100011</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>00101110001110100000000000100010</t>
+          <t>00000000000000000000000100100101</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>00100000111111000000001110010100</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>00100001011110100000000100100100</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>00101110001110100000000000100010</t>
+          <t>00000000000000000000000100100110</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>00100000111111000000001000010111</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>00100001011110100000000100100101</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>00101110001110100000000000100010</t>
+          <t>00000000000000000000000100100111</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>00100000111111000000100001110001</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>00100001011110100000000100100110</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>00101110001110100000000000100010</t>
+          <t>00000000000000000000000100101000</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>00100000111111000000001110100011</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>00100001011110100000000100100111</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>00101110001110100000000000010110</t>
+          <t>00000000000000000000000100101001</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>00100000111111000000010000100111</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>00100001011110100000000100101000</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
@@ -6987,17 +6987,17 @@
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>00101110001110100000000000010110</t>
+          <t>00000000000000000000000100101010</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>00100000111111000000101011010110</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>00100001011110100000000100101001</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
@@ -7009,61 +7009,61 @@
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>00101110001110100000000000011111</t>
+          <t>00000000000000000000000100101011</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>00100000111111000000101001100010</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>00100001011110100000000100101010</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>00101110001110100000000000011111</t>
+          <t>00000000000000000000000100101100</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>00100000111111000000101011101010</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>00100001011110100000000100101011</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>00101110001110100000000000010110</t>
+          <t>00000000000000000000000100101101</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>00100000111111000000101110001111</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>00100001011110100000000100101100</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
@@ -7075,17 +7075,17 @@
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>00101110001110100000000000010110</t>
+          <t>00000000000000000000000100101110</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>00100000111111000000001000010011</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>00100001011110100000000100101101</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
@@ -7097,17 +7097,17 @@
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>00101110001110100000000000010110</t>
+          <t>00000000000000000000000100101111</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>00100000111111000000011101000000</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>00100001011110100000000100101110</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
@@ -7119,17 +7119,17 @@
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>00101110001110100000000000010111</t>
+          <t>00000000000000000000000100110000</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>00100000111111000000100110111000</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>00100001011110100000000100101111</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
@@ -7141,17 +7141,17 @@
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>00101110001110100000000000010111</t>
+          <t>00000000000000000000000100110001</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>00100000111111000000010110010010</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>00100001011110100000000100110000</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
@@ -7163,17 +7163,17 @@
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>00101110001110100000000000011010</t>
+          <t>00000000000000000000000100110010</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>00100000111111000000011000100111</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>00100001011110100000000100110001</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
@@ -7185,17 +7185,17 @@
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>00101110001110100000000000011110</t>
+          <t>00000000000000000000000100110011</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>00100000111111000000101110101011</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>00100001011110100000000100110010</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
@@ -7207,17 +7207,17 @@
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>00101110001110100000000000011110</t>
+          <t>00000000000000000000000100110100</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>00100000111111000000010010101110</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>00100001011110100000000100110011</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
@@ -7229,17 +7229,17 @@
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>00101110001110100000000000011110</t>
+          <t>00000000000000000000000100110101</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>00100000111111000000000111000001</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>00100001011110100000000100110100</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
@@ -7251,17 +7251,17 @@
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>00101110001110100000000000011110</t>
+          <t>00000000000000000000000100110110</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>00100000111111000000011111000110</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>00100001011110100000000100110101</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
@@ -7273,17 +7273,17 @@
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>00101110001110100000000000011110</t>
+          <t>00000000000000000000000100110111</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>00100000111111000000100001010110</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>00100001011110100000000100110110</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
@@ -7295,17 +7295,17 @@
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>00101110001110100000000000011110</t>
+          <t>00000000000000000000000100111000</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>00100000111111000000101100110111</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>00100001011110100000000100110111</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
@@ -7317,17 +7317,17 @@
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>00101110001110100000000000100100</t>
+          <t>00000000000000000000000100111001</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>00100000111111000000010110000011</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>00100001011110100000000100111000</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
@@ -7339,17 +7339,17 @@
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>00101110001110100000000000100100</t>
+          <t>00000000000000000000000100111010</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>00100000111111000000000011011110</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>00100001011110100000000100111001</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
@@ -7361,17 +7361,17 @@
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>00101110001110100000000000100100</t>
+          <t>00000000000000000000000100111011</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>00100000111111000000010010000110</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>00100001011110100000000100111010</t>
+          <t>00000000000000000000000000000000</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
